--- a/data/nzd0491/nzd0491.xlsx
+++ b/data/nzd0491/nzd0491.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q451"/>
+  <dimension ref="A1:Q452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26031,10 +26031,10 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>397.65</v>
+        <v>383.63</v>
       </c>
       <c r="C450" t="n">
-        <v>418.08</v>
+        <v>398.17</v>
       </c>
       <c r="D450" t="n">
         <v>399.45</v>
@@ -26088,10 +26088,10 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>398.05</v>
+        <v>382.51</v>
       </c>
       <c r="C451" t="n">
-        <v>436.24</v>
+        <v>395.19</v>
       </c>
       <c r="D451" t="n">
         <v>399.45</v>
@@ -26135,6 +26135,63 @@
       <c r="Q451" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>380.74</v>
+      </c>
+      <c r="C452" t="n">
+        <v>391.99</v>
+      </c>
+      <c r="D452" t="n">
+        <v>396.06</v>
+      </c>
+      <c r="E452" t="n">
+        <v>389.02</v>
+      </c>
+      <c r="F452" t="n">
+        <v>376.18</v>
+      </c>
+      <c r="G452" t="n">
+        <v>374.69</v>
+      </c>
+      <c r="H452" t="n">
+        <v>378.18</v>
+      </c>
+      <c r="I452" t="n">
+        <v>370.76</v>
+      </c>
+      <c r="J452" t="n">
+        <v>359.08</v>
+      </c>
+      <c r="K452" t="n">
+        <v>369.45</v>
+      </c>
+      <c r="L452" t="n">
+        <v>362.29</v>
+      </c>
+      <c r="M452" t="n">
+        <v>360.22</v>
+      </c>
+      <c r="N452" t="n">
+        <v>360.58</v>
+      </c>
+      <c r="O452" t="n">
+        <v>388.85</v>
+      </c>
+      <c r="P452" t="n">
+        <v>399.43</v>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26149,7 +26206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B510"/>
+  <dimension ref="A1:B511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31252,6 +31309,16 @@
       </c>
       <c r="B510" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -31420,28 +31487,28 @@
         <v>0.153</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2758344763717712</v>
+        <v>-0.2841970343628524</v>
       </c>
       <c r="J2" t="n">
+        <v>451</v>
+      </c>
+      <c r="K2" t="n">
         <v>450</v>
       </c>
-      <c r="K2" t="n">
-        <v>449</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.04431326580360306</v>
+        <v>0.04837249013530065</v>
       </c>
       <c r="M2" t="n">
-        <v>7.953786020461901</v>
+        <v>7.893460831336686</v>
       </c>
       <c r="N2" t="n">
-        <v>89.51090756098097</v>
+        <v>86.90044325707508</v>
       </c>
       <c r="O2" t="n">
-        <v>9.4610204291599</v>
+        <v>9.322040723847707</v>
       </c>
       <c r="P2" t="n">
-        <v>377.4696616879534</v>
+        <v>377.5545374809925</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31498,28 +31565,28 @@
         <v>0.0901</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08885477059628021</v>
+        <v>-0.1091722273851658</v>
       </c>
       <c r="J3" t="n">
+        <v>451</v>
+      </c>
+      <c r="K3" t="n">
         <v>450</v>
       </c>
-      <c r="K3" t="n">
-        <v>449</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.004187085308518634</v>
+        <v>0.006965195428301763</v>
       </c>
       <c r="M3" t="n">
-        <v>8.22604409681243</v>
+        <v>8.106851115633591</v>
       </c>
       <c r="N3" t="n">
-        <v>102.4599518065385</v>
+        <v>92.96071316186155</v>
       </c>
       <c r="O3" t="n">
-        <v>10.12225033312941</v>
+        <v>9.64161361815861</v>
       </c>
       <c r="P3" t="n">
-        <v>379.6964158014504</v>
+        <v>379.9027654338184</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31576,28 +31643,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3755763036262613</v>
+        <v>-0.3676084991058087</v>
       </c>
       <c r="J4" t="n">
+        <v>451</v>
+      </c>
+      <c r="K4" t="n">
         <v>450</v>
       </c>
-      <c r="K4" t="n">
-        <v>449</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.06861753029873074</v>
+        <v>0.06579723934257464</v>
       </c>
       <c r="M4" t="n">
-        <v>8.691249851044816</v>
+        <v>8.704419294504147</v>
       </c>
       <c r="N4" t="n">
-        <v>104.4758819077643</v>
+        <v>104.9659648566525</v>
       </c>
       <c r="O4" t="n">
-        <v>10.22134442760659</v>
+        <v>10.24528988641378</v>
       </c>
       <c r="P4" t="n">
-        <v>387.7604646939841</v>
+        <v>387.6793597275965</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31654,28 +31721,28 @@
         <v>0.091</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3268789079104485</v>
+        <v>-0.3221686353215646</v>
       </c>
       <c r="J5" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K5" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05850454174490793</v>
+        <v>0.05703940988091405</v>
       </c>
       <c r="M5" t="n">
-        <v>7.785617275253292</v>
+        <v>7.788009609941181</v>
       </c>
       <c r="N5" t="n">
-        <v>93.72326070047379</v>
+        <v>93.76731988034268</v>
       </c>
       <c r="O5" t="n">
-        <v>9.681077455555956</v>
+        <v>9.683352718988537</v>
       </c>
       <c r="P5" t="n">
-        <v>386.8434275702932</v>
+        <v>386.7954846060119</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31732,28 +31799,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.267234021464153</v>
+        <v>-0.2680539124925403</v>
       </c>
       <c r="J6" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K6" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05152676392629674</v>
+        <v>0.05205823601212822</v>
       </c>
       <c r="M6" t="n">
-        <v>6.625009714583046</v>
+        <v>6.614501336533311</v>
       </c>
       <c r="N6" t="n">
-        <v>71.65073544183919</v>
+        <v>71.49949593721269</v>
       </c>
       <c r="O6" t="n">
-        <v>8.464675743455221</v>
+        <v>8.4557374567339</v>
       </c>
       <c r="P6" t="n">
-        <v>385.0095400346716</v>
+        <v>385.0178852005928</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31810,28 +31877,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.00722663323676863</v>
+        <v>-0.00977497902848388</v>
       </c>
       <c r="J7" t="n">
+        <v>451</v>
+      </c>
+      <c r="K7" t="n">
         <v>450</v>
       </c>
-      <c r="K7" t="n">
-        <v>449</v>
-      </c>
       <c r="L7" t="n">
-        <v>3.192195190593328e-05</v>
+        <v>5.863582447407367e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>7.061664823638973</v>
+        <v>7.059211588679421</v>
       </c>
       <c r="N7" t="n">
-        <v>89.02126953501657</v>
+        <v>88.89705343662916</v>
       </c>
       <c r="O7" t="n">
-        <v>9.435108347815438</v>
+        <v>9.428523396408854</v>
       </c>
       <c r="P7" t="n">
-        <v>380.6503433638243</v>
+        <v>380.6763323569291</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31888,28 +31955,28 @@
         <v>0.0788</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.05130627700217252</v>
+        <v>-0.05187168805732545</v>
       </c>
       <c r="J8" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K8" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001786236413566455</v>
+        <v>0.001834440275054416</v>
       </c>
       <c r="M8" t="n">
-        <v>7.314635941163615</v>
+        <v>7.301868107245964</v>
       </c>
       <c r="N8" t="n">
-        <v>80.1808330208227</v>
+        <v>80.00667770435365</v>
       </c>
       <c r="O8" t="n">
-        <v>8.954375077068343</v>
+        <v>8.944645197231338</v>
       </c>
       <c r="P8" t="n">
-        <v>380.8021825881328</v>
+        <v>380.8079375591053</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31966,28 +32033,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1471837762551709</v>
+        <v>-0.1472281227340999</v>
       </c>
       <c r="J9" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K9" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01340723641919728</v>
+        <v>0.01347891150466074</v>
       </c>
       <c r="M9" t="n">
-        <v>7.542058523080025</v>
+        <v>7.525555018614821</v>
       </c>
       <c r="N9" t="n">
-        <v>86.8887373550494</v>
+        <v>86.6961017265141</v>
       </c>
       <c r="O9" t="n">
-        <v>9.321412841144276</v>
+        <v>9.311074144614793</v>
       </c>
       <c r="P9" t="n">
-        <v>374.6991658206612</v>
+        <v>374.6996171961633</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32044,28 +32111,28 @@
         <v>0.1006</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.539132301432353</v>
+        <v>-0.5402833657002899</v>
       </c>
       <c r="J10" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K10" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1619754009862302</v>
+        <v>0.1631849034801116</v>
       </c>
       <c r="M10" t="n">
-        <v>7.397018682704268</v>
+        <v>7.386089529828032</v>
       </c>
       <c r="N10" t="n">
-        <v>81.96781424642778</v>
+        <v>81.80110874212227</v>
       </c>
       <c r="O10" t="n">
-        <v>9.053607802772758</v>
+        <v>9.044396538306039</v>
       </c>
       <c r="P10" t="n">
-        <v>375.7513045195442</v>
+        <v>375.7630204939474</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32122,28 +32189,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.363918055163902</v>
+        <v>-0.3611305313337705</v>
       </c>
       <c r="J11" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K11" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07912337666928193</v>
+        <v>0.07828025773655067</v>
       </c>
       <c r="M11" t="n">
-        <v>7.438337059134629</v>
+        <v>7.434998034650969</v>
       </c>
       <c r="N11" t="n">
-        <v>84.01344371937776</v>
+        <v>83.91537234481201</v>
       </c>
       <c r="O11" t="n">
-        <v>9.165884775589193</v>
+        <v>9.16053340940428</v>
       </c>
       <c r="P11" t="n">
-        <v>372.6054494082189</v>
+        <v>372.5770769195998</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32200,28 +32267,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6221976984090208</v>
+        <v>-0.6223261893578915</v>
       </c>
       <c r="J12" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K12" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2278953587865916</v>
+        <v>0.2288138484376179</v>
       </c>
       <c r="M12" t="n">
-        <v>6.972180711088876</v>
+        <v>6.957378845798885</v>
       </c>
       <c r="N12" t="n">
-        <v>71.48952780529477</v>
+        <v>71.33120186665685</v>
       </c>
       <c r="O12" t="n">
-        <v>8.455148006114072</v>
+        <v>8.445780121851199</v>
       </c>
       <c r="P12" t="n">
-        <v>378.8034947783972</v>
+        <v>378.8048026086461</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32278,28 +32345,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4498700291356572</v>
+        <v>-0.4536150015333998</v>
       </c>
       <c r="J13" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K13" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1051640541811542</v>
+        <v>0.1070308383149619</v>
       </c>
       <c r="M13" t="n">
-        <v>7.866812845213481</v>
+        <v>7.866486842705551</v>
       </c>
       <c r="N13" t="n">
-        <v>93.86315947707429</v>
+        <v>93.81425211425821</v>
       </c>
       <c r="O13" t="n">
-        <v>9.688300133515389</v>
+        <v>9.68577576212965</v>
       </c>
       <c r="P13" t="n">
-        <v>380.4487722595404</v>
+        <v>380.48689002757</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32356,28 +32423,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3476911854105393</v>
+        <v>-0.3536647524533273</v>
       </c>
       <c r="J14" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K14" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06810898926547526</v>
+        <v>0.07032243620719436</v>
       </c>
       <c r="M14" t="n">
-        <v>7.966314030775246</v>
+        <v>7.98073012934508</v>
       </c>
       <c r="N14" t="n">
-        <v>90.41859037693484</v>
+        <v>90.62430449731097</v>
       </c>
       <c r="O14" t="n">
-        <v>9.508869037742334</v>
+        <v>9.519679852668942</v>
       </c>
       <c r="P14" t="n">
-        <v>383.2056168501997</v>
+        <v>383.266392959241</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32434,28 +32501,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3190549402807918</v>
+        <v>-0.3153981503029374</v>
       </c>
       <c r="J15" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K15" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05105959687308037</v>
+        <v>0.05011104637634745</v>
       </c>
       <c r="M15" t="n">
-        <v>8.229804295086268</v>
+        <v>8.229115564471842</v>
       </c>
       <c r="N15" t="n">
-        <v>103.7980063610225</v>
+        <v>103.7191823631178</v>
       </c>
       <c r="O15" t="n">
-        <v>10.18813066077495</v>
+        <v>10.18426150308002</v>
       </c>
       <c r="P15" t="n">
-        <v>388.8573816029588</v>
+        <v>388.8202164811596</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32512,28 +32579,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4860768167380878</v>
+        <v>-0.4794981906812862</v>
       </c>
       <c r="J16" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K16" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08063095571054768</v>
+        <v>0.0787362247706056</v>
       </c>
       <c r="M16" t="n">
-        <v>10.01462525420198</v>
+        <v>10.02351283863443</v>
       </c>
       <c r="N16" t="n">
-        <v>147.9267364504834</v>
+        <v>148.0923978563347</v>
       </c>
       <c r="O16" t="n">
-        <v>12.16251357452412</v>
+        <v>12.16932199657544</v>
       </c>
       <c r="P16" t="n">
-        <v>397.1515292003261</v>
+        <v>397.0846489792103</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32571,7 +32638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q451"/>
+  <dimension ref="A1:Q452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71585,12 +71652,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>-45.50379293461068,166.7179326835316</t>
+          <t>-45.50388531064943,166.71805417254797</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>-45.50320704760288,166.71838204131623</t>
+          <t>-45.50333823168049,166.7185545686947</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -71672,12 +71739,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>-45.50379029905876,166.71792921737432</t>
+          <t>-45.50389269018561,166.71806387782175</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>-45.50308739382678,166.71822467902192</t>
+          <t>-45.503357866445604,166.7185803915456</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -71748,6 +71815,93 @@
       <c r="Q451" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>-45.5039043524869,166.7180792156257</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>-45.5033789507516,166.7186081208014</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>-45.502900853751434,166.7191992438057</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-45.50249595475743,166.71988663920033</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>-45.50212926637432,166.72062429384792</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>-45.50169158213492,166.72125713744904</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>-45.50122235777546,166.72179579172533</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>-45.5007600167483,166.72235695195067</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>-45.50030428053139,166.7229829528233</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>-45.49972825012922,166.72338550815996</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>-45.49924873548212,166.72396453582905</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>-45.49873964883832,166.72447964517684</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>-45.498203524801234,166.72494189334702</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>-45.49752284418955,166.7251139203201</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>-45.496932124835574,166.72547195489884</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0491/nzd0491.xlsx
+++ b/data/nzd0491/nzd0491.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q452"/>
+  <dimension ref="A1:Q455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26181,7 +26181,7 @@
         <v>360.22</v>
       </c>
       <c r="N452" t="n">
-        <v>360.58</v>
+        <v>361.86</v>
       </c>
       <c r="O452" t="n">
         <v>388.85</v>
@@ -26192,6 +26192,177 @@
       <c r="Q452" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:27:19+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>379.37</v>
+      </c>
+      <c r="C453" t="n">
+        <v>390.18</v>
+      </c>
+      <c r="D453" t="n">
+        <v>394.18</v>
+      </c>
+      <c r="E453" t="n">
+        <v>387.87</v>
+      </c>
+      <c r="F453" t="n">
+        <v>375.71</v>
+      </c>
+      <c r="G453" t="n">
+        <v>373.17</v>
+      </c>
+      <c r="H453" t="n">
+        <v>376.56</v>
+      </c>
+      <c r="I453" t="n">
+        <v>368.75</v>
+      </c>
+      <c r="J453" t="n">
+        <v>357.4</v>
+      </c>
+      <c r="K453" t="n">
+        <v>361.96</v>
+      </c>
+      <c r="L453" t="n">
+        <v>360.87</v>
+      </c>
+      <c r="M453" t="n">
+        <v>359.54</v>
+      </c>
+      <c r="N453" t="n">
+        <v>362.52</v>
+      </c>
+      <c r="O453" t="n">
+        <v>386.09</v>
+      </c>
+      <c r="P453" t="n">
+        <v>395.64</v>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:33:29+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>379.11</v>
+      </c>
+      <c r="C454" t="n">
+        <v>389.44</v>
+      </c>
+      <c r="D454" t="n">
+        <v>392.06</v>
+      </c>
+      <c r="E454" t="n">
+        <v>388.44</v>
+      </c>
+      <c r="F454" t="n">
+        <v>377.19</v>
+      </c>
+      <c r="G454" t="n">
+        <v>372.37</v>
+      </c>
+      <c r="H454" t="n">
+        <v>374.4</v>
+      </c>
+      <c r="I454" t="n">
+        <v>367.01</v>
+      </c>
+      <c r="J454" t="n">
+        <v>358.46</v>
+      </c>
+      <c r="K454" t="n">
+        <v>362.18</v>
+      </c>
+      <c r="L454" t="n">
+        <v>360.86</v>
+      </c>
+      <c r="M454" t="n">
+        <v>360.38</v>
+      </c>
+      <c r="N454" t="n">
+        <v>363.6</v>
+      </c>
+      <c r="O454" t="n">
+        <v>390.12</v>
+      </c>
+      <c r="P454" t="n">
+        <v>397.31</v>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-28 22:33:34+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>377.16</v>
+      </c>
+      <c r="C455" t="n">
+        <v>388.72</v>
+      </c>
+      <c r="D455" t="n">
+        <v>390.21</v>
+      </c>
+      <c r="E455" t="n">
+        <v>387.98</v>
+      </c>
+      <c r="F455" t="n">
+        <v>377</v>
+      </c>
+      <c r="G455" t="n">
+        <v>371.67</v>
+      </c>
+      <c r="H455" t="n">
+        <v>373.63</v>
+      </c>
+      <c r="I455" t="n">
+        <v>366.28</v>
+      </c>
+      <c r="J455" t="n">
+        <v>359.22</v>
+      </c>
+      <c r="K455" t="n">
+        <v>361.89</v>
+      </c>
+      <c r="L455" t="n">
+        <v>360.62</v>
+      </c>
+      <c r="M455" t="n">
+        <v>361.53</v>
+      </c>
+      <c r="N455" t="n">
+        <v>366.06</v>
+      </c>
+      <c r="O455" t="n">
+        <v>391.61</v>
+      </c>
+      <c r="P455" t="n">
+        <v>398.47</v>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26206,7 +26377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B511"/>
+  <dimension ref="A1:B514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31319,6 +31490,36 @@
       </c>
       <c r="B511" t="n">
         <v>-0.54</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2025-12-28 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>-0.47</v>
       </c>
     </row>
   </sheetData>
@@ -31487,28 +31688,28 @@
         <v>0.153</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2841970343628524</v>
+        <v>-0.273261738332645</v>
       </c>
       <c r="J2" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K2" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04837249013530065</v>
+        <v>0.04526772390217948</v>
       </c>
       <c r="M2" t="n">
-        <v>7.893460831336686</v>
+        <v>7.896022305519262</v>
       </c>
       <c r="N2" t="n">
-        <v>86.90044325707508</v>
+        <v>86.79039426693673</v>
       </c>
       <c r="O2" t="n">
-        <v>9.322040723847707</v>
+        <v>9.316136230591345</v>
       </c>
       <c r="P2" t="n">
-        <v>377.5545374809925</v>
+        <v>377.4429669531211</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31565,28 +31766,28 @@
         <v>0.0901</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1091722273851658</v>
+        <v>-0.09306057219032411</v>
       </c>
       <c r="J3" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K3" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006965195428301763</v>
+        <v>0.005088378513915415</v>
       </c>
       <c r="M3" t="n">
-        <v>8.106851115633591</v>
+        <v>8.131634451716184</v>
       </c>
       <c r="N3" t="n">
-        <v>92.96071316186155</v>
+        <v>93.344123560425</v>
       </c>
       <c r="O3" t="n">
-        <v>9.64161361815861</v>
+        <v>9.661476261960436</v>
       </c>
       <c r="P3" t="n">
-        <v>379.9027654338184</v>
+        <v>379.7384049846515</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31643,28 +31844,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3676084991058087</v>
+        <v>-0.3493261807793012</v>
       </c>
       <c r="J4" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K4" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06579723934257464</v>
+        <v>0.05990152533311532</v>
       </c>
       <c r="M4" t="n">
-        <v>8.704419294504147</v>
+        <v>8.721105649093834</v>
       </c>
       <c r="N4" t="n">
-        <v>104.9659648566525</v>
+        <v>105.5718640004607</v>
       </c>
       <c r="O4" t="n">
-        <v>10.24528988641378</v>
+        <v>10.27481698136082</v>
       </c>
       <c r="P4" t="n">
-        <v>387.6793597275965</v>
+        <v>387.4928701962139</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31721,28 +31922,28 @@
         <v>0.091</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3221686353215646</v>
+        <v>-0.3095420166130727</v>
       </c>
       <c r="J5" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K5" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05703940988091405</v>
+        <v>0.05327651885247997</v>
       </c>
       <c r="M5" t="n">
-        <v>7.788009609941181</v>
+        <v>7.789918922716713</v>
       </c>
       <c r="N5" t="n">
-        <v>93.76731988034268</v>
+        <v>93.758844227917</v>
       </c>
       <c r="O5" t="n">
-        <v>9.683352718988537</v>
+        <v>9.682915068713399</v>
       </c>
       <c r="P5" t="n">
-        <v>386.7954846060119</v>
+        <v>386.6666787196444</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31799,28 +32000,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2680539124925403</v>
+        <v>-0.2698502384092938</v>
       </c>
       <c r="J6" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K6" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05205823601212822</v>
+        <v>0.05342787882097288</v>
       </c>
       <c r="M6" t="n">
-        <v>6.614501336533311</v>
+        <v>6.579858164842552</v>
       </c>
       <c r="N6" t="n">
-        <v>71.49949593721269</v>
+        <v>71.04231582246409</v>
       </c>
       <c r="O6" t="n">
-        <v>8.4557374567339</v>
+        <v>8.428660381250634</v>
       </c>
       <c r="P6" t="n">
-        <v>385.0178852005928</v>
+        <v>385.0362028065404</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31877,28 +32078,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.00977497902848388</v>
+        <v>-0.0202158920487535</v>
       </c>
       <c r="J7" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K7" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L7" t="n">
-        <v>5.863582447407367e-05</v>
+        <v>0.0002531474016735924</v>
       </c>
       <c r="M7" t="n">
-        <v>7.059211588679421</v>
+        <v>7.066648590007241</v>
       </c>
       <c r="N7" t="n">
-        <v>88.89705343662916</v>
+        <v>88.72760454875971</v>
       </c>
       <c r="O7" t="n">
-        <v>9.428523396408854</v>
+        <v>9.419533138577501</v>
       </c>
       <c r="P7" t="n">
-        <v>380.6763323569291</v>
+        <v>380.7830604285732</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31955,28 +32156,28 @@
         <v>0.0788</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.05187168805732545</v>
+        <v>-0.05783719497979821</v>
       </c>
       <c r="J8" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K8" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001834440275054416</v>
+        <v>0.002308080078810781</v>
       </c>
       <c r="M8" t="n">
-        <v>7.301868107245964</v>
+        <v>7.289639232885033</v>
       </c>
       <c r="N8" t="n">
-        <v>80.00667770435365</v>
+        <v>79.62432203006529</v>
       </c>
       <c r="O8" t="n">
-        <v>8.944645197231338</v>
+        <v>8.923246159894127</v>
       </c>
       <c r="P8" t="n">
-        <v>380.8079375591053</v>
+        <v>380.8688101376347</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32033,28 +32234,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1472281227340999</v>
+        <v>-0.1517921827695892</v>
       </c>
       <c r="J9" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K9" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01347891150466074</v>
+        <v>0.01450381076870944</v>
       </c>
       <c r="M9" t="n">
-        <v>7.525555018614821</v>
+        <v>7.498148575554435</v>
       </c>
       <c r="N9" t="n">
-        <v>86.6961017265141</v>
+        <v>86.20994291835234</v>
       </c>
       <c r="O9" t="n">
-        <v>9.311074144614793</v>
+        <v>9.284930959266866</v>
       </c>
       <c r="P9" t="n">
-        <v>374.6996171961633</v>
+        <v>374.7461907293676</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32111,28 +32312,28 @@
         <v>0.1006</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5402833657002899</v>
+        <v>-0.5445596772790366</v>
       </c>
       <c r="J10" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K10" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1631849034801116</v>
+        <v>0.1672020223443409</v>
       </c>
       <c r="M10" t="n">
-        <v>7.386089529828032</v>
+        <v>7.357792492225142</v>
       </c>
       <c r="N10" t="n">
-        <v>81.80110874212227</v>
+        <v>81.33450298158218</v>
       </c>
       <c r="O10" t="n">
-        <v>9.044396538306039</v>
+        <v>9.018564352577531</v>
       </c>
       <c r="P10" t="n">
-        <v>375.7630204939474</v>
+        <v>375.8066321284488</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32189,28 +32390,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3611305313337705</v>
+        <v>-0.3626071796226265</v>
       </c>
       <c r="J11" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K11" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07828025773655067</v>
+        <v>0.07990686290709426</v>
       </c>
       <c r="M11" t="n">
-        <v>7.434998034650969</v>
+        <v>7.393679585412913</v>
       </c>
       <c r="N11" t="n">
-        <v>83.91537234481201</v>
+        <v>83.36931421283094</v>
       </c>
       <c r="O11" t="n">
-        <v>9.16053340940428</v>
+        <v>9.130679833004272</v>
       </c>
       <c r="P11" t="n">
-        <v>372.5770769195998</v>
+        <v>372.5921411485146</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32267,28 +32468,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6223261893578915</v>
+        <v>-0.6246231252107358</v>
       </c>
       <c r="J12" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K12" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2288138484376179</v>
+        <v>0.2326038977599069</v>
       </c>
       <c r="M12" t="n">
-        <v>6.957378845798885</v>
+        <v>6.923026038717334</v>
       </c>
       <c r="N12" t="n">
-        <v>71.33120186665685</v>
+        <v>70.88011928046218</v>
       </c>
       <c r="O12" t="n">
-        <v>8.445780121851199</v>
+        <v>8.419033155918925</v>
       </c>
       <c r="P12" t="n">
-        <v>378.8048026086461</v>
+        <v>378.8282354605635</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32345,28 +32546,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4536150015333998</v>
+        <v>-0.4642130499371964</v>
       </c>
       <c r="J13" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K13" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1070308383149619</v>
+        <v>0.1124825983425952</v>
       </c>
       <c r="M13" t="n">
-        <v>7.866486842705551</v>
+        <v>7.862403817622142</v>
       </c>
       <c r="N13" t="n">
-        <v>93.81425211425821</v>
+        <v>93.62933703051765</v>
       </c>
       <c r="O13" t="n">
-        <v>9.68577576212965</v>
+        <v>9.676225350337685</v>
       </c>
       <c r="P13" t="n">
-        <v>380.48689002757</v>
+        <v>380.5949890132231</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32423,28 +32624,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3536647524533273</v>
+        <v>-0.3660603058577399</v>
       </c>
       <c r="J14" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K14" t="n">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07032243620719436</v>
+        <v>0.07549956756212706</v>
       </c>
       <c r="M14" t="n">
-        <v>7.98073012934508</v>
+        <v>7.994531047465762</v>
       </c>
       <c r="N14" t="n">
-        <v>90.62430449731097</v>
+        <v>90.61174966086296</v>
       </c>
       <c r="O14" t="n">
-        <v>9.519679852668942</v>
+        <v>9.519020414982991</v>
       </c>
       <c r="P14" t="n">
-        <v>383.266392959241</v>
+        <v>383.3927802346323</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32501,28 +32702,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3153981503029374</v>
+        <v>-0.3041067266986814</v>
       </c>
       <c r="J15" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K15" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05011104637634745</v>
+        <v>0.04715898338973035</v>
       </c>
       <c r="M15" t="n">
-        <v>8.229115564471842</v>
+        <v>8.22871687631989</v>
       </c>
       <c r="N15" t="n">
-        <v>103.7191823631178</v>
+        <v>103.5569662022126</v>
       </c>
       <c r="O15" t="n">
-        <v>10.18426150308002</v>
+        <v>10.17629432564785</v>
       </c>
       <c r="P15" t="n">
-        <v>388.8202164811596</v>
+        <v>388.7051641912686</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32579,28 +32780,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4794981906812862</v>
+        <v>-0.4631561831975904</v>
       </c>
       <c r="J16" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K16" t="n">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0787362247706056</v>
+        <v>0.07433954539936183</v>
       </c>
       <c r="M16" t="n">
-        <v>10.02351283863443</v>
+        <v>10.03682819262452</v>
       </c>
       <c r="N16" t="n">
-        <v>148.0923978563347</v>
+        <v>148.1471106223575</v>
       </c>
       <c r="O16" t="n">
-        <v>12.16932199657544</v>
+        <v>12.1715697682081</v>
       </c>
       <c r="P16" t="n">
-        <v>397.0846489792103</v>
+        <v>396.9181153622616</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32638,7 +32839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q452"/>
+  <dimension ref="A1:Q455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71886,7 +72087,7 @@
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t>-45.498203524801234,166.72494189334702</t>
+          <t>-45.498197015131424,166.72492843443612</t>
         </is>
       </c>
       <c r="O452" t="inlineStr">
@@ -71902,6 +72103,267 @@
       <c r="Q452" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:27:19+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>-45.50391337923866,166.7180910872636</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>-45.50339087655966,166.7186238051709</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>-45.50291324072301,166.71921553472015</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-45.50250353185344,166.71989660439218</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>-45.50213236308227,166.720628366586</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>-45.501701418044455,166.72127057874346</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>-45.50123194072571,166.7218113397668</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>-45.50077098197368,166.7223773205298</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>-45.50031344542565,166.72299997726154</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>-45.499769110083676,166.72346140829075</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>-45.49925641987311,166.72397899248497</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>-45.49874320361702,166.7244866989296</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>-45.49819365858236,166.72492149468644</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>-45.49753688064013,166.72514294078312</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>-45.49695139943887,166.7255118051517</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:33:29+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>-45.50391509234473,166.7180933402756</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>-45.50339575230388,166.71863021756695</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>-45.502927209007744,166.7192339053344</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-45.50249977624942,166.71989166512282</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>-45.502122611746145,166.7206155417953</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>-45.50170659483842,166.7212776531108</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>-45.50124471798982,166.72183207049707</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>-45.50078047425571,166.7223949530377</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>-45.500307662814066,166.72298923565103</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>-45.499767909925446,166.72345917891278</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>-45.499256473988545,166.72397909429242</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>-45.49873881241973,166.72447798547046</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>-45.49818816604672,166.72491013873426</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>-45.49751638538576,166.72510056670626</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>-45.496942906409416,166.725494245802</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-28 22:33:34+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>-45.50392794063896,166.71811023786998</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>-45.50340049627092,166.7186364566561</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>-45.50293939831075,166.71924993630233</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-45.502502807087765,166.71989565119978</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>-45.502123863606926,166.72061718822087</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>-45.501711124532825,166.7212838431833</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>-45.50124927284706,166.72183946062083</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>-45.50078445664919,166.72240235058595</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>-45.5003035167901,166.72298153412035</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>-45.49976949195219,166.7234621176383</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>-45.499257772758675,166.7239815376713</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>-45.49873280066059,166.72446605633226</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>-45.498175655267254,166.72488427240725</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>-45.49750880773229,166.725084899872</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>-45.496937007058186,166.72548204889162</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0491/nzd0491.xlsx
+++ b/data/nzd0491/nzd0491.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q455"/>
+  <dimension ref="A1:Q457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26363,6 +26363,120 @@
       <c r="Q455" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:27:11+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>376.15</v>
+      </c>
+      <c r="C456" t="n">
+        <v>387.89</v>
+      </c>
+      <c r="D456" t="n">
+        <v>390.11</v>
+      </c>
+      <c r="E456" t="n">
+        <v>388</v>
+      </c>
+      <c r="F456" t="n">
+        <v>377.19</v>
+      </c>
+      <c r="G456" t="n">
+        <v>371.34</v>
+      </c>
+      <c r="H456" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="I456" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="J456" t="n">
+        <v>359.57</v>
+      </c>
+      <c r="K456" t="n">
+        <v>361.24</v>
+      </c>
+      <c r="L456" t="n">
+        <v>359.85</v>
+      </c>
+      <c r="M456" t="n">
+        <v>361.14</v>
+      </c>
+      <c r="N456" t="n">
+        <v>366.76</v>
+      </c>
+      <c r="O456" t="n">
+        <v>390.63</v>
+      </c>
+      <c r="P456" t="n">
+        <v>398.36</v>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-14 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="C457" t="n">
+        <v>384.24</v>
+      </c>
+      <c r="D457" t="n">
+        <v>386.54</v>
+      </c>
+      <c r="E457" t="n">
+        <v>387.43</v>
+      </c>
+      <c r="F457" t="n">
+        <v>377.16</v>
+      </c>
+      <c r="G457" t="n">
+        <v>369.21</v>
+      </c>
+      <c r="H457" t="n">
+        <v>368.01</v>
+      </c>
+      <c r="I457" t="n">
+        <v>361.78</v>
+      </c>
+      <c r="J457" t="n">
+        <v>358.69</v>
+      </c>
+      <c r="K457" t="n">
+        <v>358.87</v>
+      </c>
+      <c r="L457" t="n">
+        <v>360.96</v>
+      </c>
+      <c r="M457" t="n">
+        <v>360.99</v>
+      </c>
+      <c r="N457" t="n">
+        <v>366.8</v>
+      </c>
+      <c r="O457" t="n">
+        <v>389.54</v>
+      </c>
+      <c r="P457" t="n">
+        <v>396.92</v>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26377,7 +26491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B514"/>
+  <dimension ref="A1:B516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31520,6 +31634,26 @@
       </c>
       <c r="B514" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-01-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -31688,28 +31822,28 @@
         <v>0.153</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.273261738332645</v>
+        <v>-0.2703380441829667</v>
       </c>
       <c r="J2" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K2" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04526772390217948</v>
+        <v>0.04470896642717315</v>
       </c>
       <c r="M2" t="n">
-        <v>7.896022305519262</v>
+        <v>7.87584848582505</v>
       </c>
       <c r="N2" t="n">
-        <v>86.79039426693673</v>
+        <v>86.48548612282119</v>
       </c>
       <c r="O2" t="n">
-        <v>9.316136230591345</v>
+        <v>9.299757315264801</v>
       </c>
       <c r="P2" t="n">
-        <v>377.4429669531211</v>
+        <v>377.4130722594371</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31766,28 +31900,28 @@
         <v>0.0901</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09306057219032411</v>
+        <v>-0.08553259476019039</v>
       </c>
       <c r="J3" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K3" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005088378513915415</v>
+        <v>0.004326161104032389</v>
       </c>
       <c r="M3" t="n">
-        <v>8.131634451716184</v>
+        <v>8.133241972509083</v>
       </c>
       <c r="N3" t="n">
-        <v>93.344123560425</v>
+        <v>93.28134299969292</v>
       </c>
       <c r="O3" t="n">
-        <v>9.661476261960436</v>
+        <v>9.658226700574641</v>
       </c>
       <c r="P3" t="n">
-        <v>379.7384049846515</v>
+        <v>379.6614090456495</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31844,28 +31978,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3493261807793012</v>
+        <v>-0.340755631998248</v>
       </c>
       <c r="J4" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K4" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05990152533311532</v>
+        <v>0.05744332322991319</v>
       </c>
       <c r="M4" t="n">
-        <v>8.721105649093834</v>
+        <v>8.717321536167992</v>
       </c>
       <c r="N4" t="n">
-        <v>105.5718640004607</v>
+        <v>105.5531236910065</v>
       </c>
       <c r="O4" t="n">
-        <v>10.27481698136082</v>
+        <v>10.27390498744302</v>
       </c>
       <c r="P4" t="n">
-        <v>387.4928701962139</v>
+        <v>387.4052081969438</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31922,28 +32056,28 @@
         <v>0.091</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3095420166130727</v>
+        <v>-0.30168197399762</v>
       </c>
       <c r="J5" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K5" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05327651885247997</v>
+        <v>0.05100781286018397</v>
       </c>
       <c r="M5" t="n">
-        <v>7.789918922716713</v>
+        <v>7.788929358814977</v>
       </c>
       <c r="N5" t="n">
-        <v>93.758844227917</v>
+        <v>93.70988664479025</v>
       </c>
       <c r="O5" t="n">
-        <v>9.682915068713399</v>
+        <v>9.680386699135022</v>
       </c>
       <c r="P5" t="n">
-        <v>386.6666787196444</v>
+        <v>386.5862787940469</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32000,28 +32134,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2698502384092938</v>
+        <v>-0.2705371999206607</v>
       </c>
       <c r="J6" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K6" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05342787882097288</v>
+        <v>0.05416338114333963</v>
       </c>
       <c r="M6" t="n">
-        <v>6.579858164842552</v>
+        <v>6.554427802545489</v>
       </c>
       <c r="N6" t="n">
-        <v>71.04231582246409</v>
+        <v>70.73349110751744</v>
       </c>
       <c r="O6" t="n">
-        <v>8.428660381250634</v>
+        <v>8.410320511580842</v>
       </c>
       <c r="P6" t="n">
-        <v>385.0362028065404</v>
+        <v>385.0432299756624</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32078,28 +32212,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0202158920487535</v>
+        <v>-0.02881085201031732</v>
       </c>
       <c r="J7" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K7" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002531474016735924</v>
+        <v>0.0005163293065125751</v>
       </c>
       <c r="M7" t="n">
-        <v>7.066648590007241</v>
+        <v>7.079771590374662</v>
       </c>
       <c r="N7" t="n">
-        <v>88.72760454875971</v>
+        <v>88.77442249600784</v>
       </c>
       <c r="O7" t="n">
-        <v>9.419533138577501</v>
+        <v>9.422017963048459</v>
       </c>
       <c r="P7" t="n">
-        <v>380.7830604285732</v>
+        <v>380.8711628138221</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32156,28 +32290,28 @@
         <v>0.0788</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.05783719497979821</v>
+        <v>-0.06518729892536362</v>
       </c>
       <c r="J8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002308080078810781</v>
+        <v>0.002944787729227349</v>
       </c>
       <c r="M8" t="n">
-        <v>7.289639232885033</v>
+        <v>7.302010444300135</v>
       </c>
       <c r="N8" t="n">
-        <v>79.62432203006529</v>
+        <v>79.62545757559668</v>
       </c>
       <c r="O8" t="n">
-        <v>8.923246159894127</v>
+        <v>8.923309788166982</v>
       </c>
       <c r="P8" t="n">
-        <v>380.8688101376347</v>
+        <v>380.9440210263114</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32234,28 +32368,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1517921827695892</v>
+        <v>-0.1576593061796221</v>
       </c>
       <c r="J9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K9" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01450381076870944</v>
+        <v>0.01573413031029469</v>
       </c>
       <c r="M9" t="n">
-        <v>7.498148575554435</v>
+        <v>7.494272669759</v>
       </c>
       <c r="N9" t="n">
-        <v>86.20994291835234</v>
+        <v>86.05372225136182</v>
       </c>
       <c r="O9" t="n">
-        <v>9.284930959266866</v>
+        <v>9.276514552964482</v>
       </c>
       <c r="P9" t="n">
-        <v>374.7461907293676</v>
+        <v>374.8062262024384</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32312,28 +32446,28 @@
         <v>0.1006</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5445596772790366</v>
+        <v>-0.5466413212376799</v>
       </c>
       <c r="J10" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K10" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1672020223443409</v>
+        <v>0.1695419397398802</v>
       </c>
       <c r="M10" t="n">
-        <v>7.357792492225142</v>
+        <v>7.33544787845919</v>
       </c>
       <c r="N10" t="n">
-        <v>81.33450298158218</v>
+        <v>81.00395563485628</v>
       </c>
       <c r="O10" t="n">
-        <v>9.018564352577531</v>
+        <v>9.000219754809118</v>
       </c>
       <c r="P10" t="n">
-        <v>375.8066321284488</v>
+        <v>375.8279296277311</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32390,28 +32524,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3626071796226265</v>
+        <v>-0.365225104640941</v>
       </c>
       <c r="J11" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K11" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07990686290709426</v>
+        <v>0.08163190536192455</v>
       </c>
       <c r="M11" t="n">
-        <v>7.393679585412913</v>
+        <v>7.374949631178083</v>
       </c>
       <c r="N11" t="n">
-        <v>83.36931421283094</v>
+        <v>83.04985022708713</v>
       </c>
       <c r="O11" t="n">
-        <v>9.130679833004272</v>
+        <v>9.113169055113985</v>
       </c>
       <c r="P11" t="n">
-        <v>372.5921411485146</v>
+        <v>372.6189310314011</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32468,28 +32602,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6246231252107358</v>
+        <v>-0.6264053253520593</v>
       </c>
       <c r="J12" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K12" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2326038977599069</v>
+        <v>0.2352593878117935</v>
       </c>
       <c r="M12" t="n">
-        <v>6.923026038717334</v>
+        <v>6.90159429446634</v>
       </c>
       <c r="N12" t="n">
-        <v>70.88011928046218</v>
+        <v>70.58929257022811</v>
       </c>
       <c r="O12" t="n">
-        <v>8.419033155918925</v>
+        <v>8.401743424446387</v>
       </c>
       <c r="P12" t="n">
-        <v>378.8282354605635</v>
+        <v>378.846460993181</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32546,28 +32680,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4642130499371964</v>
+        <v>-0.4705539036833158</v>
       </c>
       <c r="J13" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K13" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1124825983425952</v>
+        <v>0.115923272978304</v>
       </c>
       <c r="M13" t="n">
-        <v>7.862403817622142</v>
+        <v>7.856270525791495</v>
       </c>
       <c r="N13" t="n">
-        <v>93.62933703051765</v>
+        <v>93.45420345609563</v>
       </c>
       <c r="O13" t="n">
-        <v>9.676225350337685</v>
+        <v>9.667171429952798</v>
       </c>
       <c r="P13" t="n">
-        <v>380.5949890132231</v>
+        <v>380.659851825076</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32624,28 +32758,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3660603058577399</v>
+        <v>-0.3720997537893597</v>
       </c>
       <c r="J14" t="n">
+        <v>456</v>
+      </c>
+      <c r="K14" t="n">
         <v>454</v>
       </c>
-      <c r="K14" t="n">
-        <v>452</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.07549956756212706</v>
+        <v>0.07832028207519581</v>
       </c>
       <c r="M14" t="n">
-        <v>7.994531047465762</v>
+        <v>7.991569611026502</v>
       </c>
       <c r="N14" t="n">
-        <v>90.61174966086296</v>
+        <v>90.42727491176051</v>
       </c>
       <c r="O14" t="n">
-        <v>9.519020414982991</v>
+        <v>9.509325681233161</v>
       </c>
       <c r="P14" t="n">
-        <v>383.3927802346323</v>
+        <v>383.4545356288852</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32702,28 +32836,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3041067266986814</v>
+        <v>-0.2960841730413954</v>
       </c>
       <c r="J15" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K15" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04715898338973035</v>
+        <v>0.04505686055494362</v>
       </c>
       <c r="M15" t="n">
-        <v>8.22871687631989</v>
+        <v>8.230733767453144</v>
       </c>
       <c r="N15" t="n">
-        <v>103.5569662022126</v>
+        <v>103.4809983982151</v>
       </c>
       <c r="O15" t="n">
-        <v>10.17629432564785</v>
+        <v>10.17256105404215</v>
       </c>
       <c r="P15" t="n">
-        <v>388.7051641912686</v>
+        <v>388.623219912908</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32780,28 +32914,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4631561831975904</v>
+        <v>-0.4521224127388931</v>
       </c>
       <c r="J16" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K16" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07433954539936183</v>
+        <v>0.07138365902786059</v>
       </c>
       <c r="M16" t="n">
-        <v>10.03682819262452</v>
+        <v>10.04722291999455</v>
       </c>
       <c r="N16" t="n">
-        <v>148.1471106223575</v>
+        <v>148.214259860967</v>
       </c>
       <c r="O16" t="n">
-        <v>12.1715697682081</v>
+        <v>12.17432790181729</v>
       </c>
       <c r="P16" t="n">
-        <v>396.9181153622616</v>
+        <v>396.8053788888529</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32839,7 +32973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q455"/>
+  <dimension ref="A1:Q457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72367,6 +72501,180 @@
         </is>
       </c>
     </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:27:11+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>-45.50393459539566,166.71811898996037</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>-45.50340596501036,166.71864364894068</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>-45.50294005719194,166.71925080284134</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>-45.50250267531218,166.7198954778921</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>-45.502122611746145,166.7206155417953</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>-45.50171325996009,166.7212867613607</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>-45.501249391155035,166.72183965257213</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>-45.50078532950249,166.72240397196651</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>-45.500301607436796,166.7229779873632</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>-45.49977303787398,166.72346870443744</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>-45.49926193964591,166.72398937684594</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>-45.4987348394312,166.7244701018658</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>-45.498172095288396,166.72487691207246</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>-45.49751379169251,166.7250952042323</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>-45.496937566479474,166.7254832054951</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-14 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>-45.503966880840856,166.71816145062604</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>-45.503430014281605,166.71867527767864</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>-45.502963579246796,166.7192817382971</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>-45.50250643091606,166.7199004171619</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>-45.50212280940837,166.72061580175722</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>-45.50172704317091,166.72130559687457</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>-45.50128251737683,166.72189339896332</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>-45.50080900564055,166.72244795193427</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>-45.50030640809632,166.7229869049245</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>-45.499785966847504,166.7234927209276</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>-45.49925593283429,166.72397807621795</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>-45.49873562357372,166.72447165784033</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>-45.49817189186102,166.72487649148192</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>-45.49751933507585,166.7251066652067</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>-45.496944889811715,166.72549834648797</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0491/nzd0491.xlsx
+++ b/data/nzd0491/nzd0491.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q457"/>
+  <dimension ref="A1:Q462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26477,6 +26477,291 @@
       <c r="Q457" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-21 22:32:52+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>370.21</v>
+      </c>
+      <c r="C458" t="n">
+        <v>381.2</v>
+      </c>
+      <c r="D458" t="n">
+        <v>385.67</v>
+      </c>
+      <c r="E458" t="n">
+        <v>386.14</v>
+      </c>
+      <c r="F458" t="n">
+        <v>378.14</v>
+      </c>
+      <c r="G458" t="n">
+        <v>367.77</v>
+      </c>
+      <c r="H458" t="n">
+        <v>365.52</v>
+      </c>
+      <c r="I458" t="n">
+        <v>358</v>
+      </c>
+      <c r="J458" t="n">
+        <v>355.08</v>
+      </c>
+      <c r="K458" t="n">
+        <v>354.85</v>
+      </c>
+      <c r="L458" t="n">
+        <v>357.73</v>
+      </c>
+      <c r="M458" t="n">
+        <v>363.46</v>
+      </c>
+      <c r="N458" t="n">
+        <v>366.84</v>
+      </c>
+      <c r="O458" t="n">
+        <v>387.67</v>
+      </c>
+      <c r="P458" t="n">
+        <v>395.65</v>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:27:12+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>366.77</v>
+      </c>
+      <c r="C459" t="n">
+        <v>377.24</v>
+      </c>
+      <c r="D459" t="n">
+        <v>384.17</v>
+      </c>
+      <c r="E459" t="n">
+        <v>386.03</v>
+      </c>
+      <c r="F459" t="n">
+        <v>377.69</v>
+      </c>
+      <c r="G459" t="n">
+        <v>365.42</v>
+      </c>
+      <c r="H459" t="n">
+        <v>363.6</v>
+      </c>
+      <c r="I459" t="n">
+        <v>355.61</v>
+      </c>
+      <c r="J459" t="n">
+        <v>353.02</v>
+      </c>
+      <c r="K459" t="n">
+        <v>352.7</v>
+      </c>
+      <c r="L459" t="n">
+        <v>354.72</v>
+      </c>
+      <c r="M459" t="n">
+        <v>360.43</v>
+      </c>
+      <c r="N459" t="n">
+        <v>364.54</v>
+      </c>
+      <c r="O459" t="n">
+        <v>387.67</v>
+      </c>
+      <c r="P459" t="n">
+        <v>398.24</v>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-14 22:33:20+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>365.73</v>
+      </c>
+      <c r="C460" t="n">
+        <v>375.49</v>
+      </c>
+      <c r="D460" t="n">
+        <v>383.28</v>
+      </c>
+      <c r="E460" t="n">
+        <v>385.81</v>
+      </c>
+      <c r="F460" t="n">
+        <v>377.01</v>
+      </c>
+      <c r="G460" t="n">
+        <v>365.11</v>
+      </c>
+      <c r="H460" t="n">
+        <v>363.83</v>
+      </c>
+      <c r="I460" t="n">
+        <v>355.63</v>
+      </c>
+      <c r="J460" t="n">
+        <v>351.96</v>
+      </c>
+      <c r="K460" t="n">
+        <v>351.88</v>
+      </c>
+      <c r="L460" t="n">
+        <v>354.08</v>
+      </c>
+      <c r="M460" t="n">
+        <v>360.18</v>
+      </c>
+      <c r="N460" t="n">
+        <v>365.49</v>
+      </c>
+      <c r="O460" t="n">
+        <v>387.8</v>
+      </c>
+      <c r="P460" t="n">
+        <v>398.76</v>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-15 22:26:59+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>365.62</v>
+      </c>
+      <c r="C461" t="n">
+        <v>374.77</v>
+      </c>
+      <c r="D461" t="n">
+        <v>383.37</v>
+      </c>
+      <c r="E461" t="n">
+        <v>386</v>
+      </c>
+      <c r="F461" t="n">
+        <v>376.28</v>
+      </c>
+      <c r="G461" t="n">
+        <v>365.47</v>
+      </c>
+      <c r="H461" t="n">
+        <v>364.48</v>
+      </c>
+      <c r="I461" t="n">
+        <v>356.24</v>
+      </c>
+      <c r="J461" t="n">
+        <v>351.43</v>
+      </c>
+      <c r="K461" t="n">
+        <v>351.58</v>
+      </c>
+      <c r="L461" t="n">
+        <v>354.08</v>
+      </c>
+      <c r="M461" t="n">
+        <v>360.75</v>
+      </c>
+      <c r="N461" t="n">
+        <v>366.85</v>
+      </c>
+      <c r="O461" t="n">
+        <v>388.83</v>
+      </c>
+      <c r="P461" t="n">
+        <v>399.36</v>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>365.2</v>
+      </c>
+      <c r="C462" t="n">
+        <v>374.69</v>
+      </c>
+      <c r="D462" t="n">
+        <v>382.6</v>
+      </c>
+      <c r="E462" t="n">
+        <v>385.85</v>
+      </c>
+      <c r="F462" t="n">
+        <v>376.94</v>
+      </c>
+      <c r="G462" t="n">
+        <v>366.45</v>
+      </c>
+      <c r="H462" t="n">
+        <v>364.96</v>
+      </c>
+      <c r="I462" t="n">
+        <v>356.25</v>
+      </c>
+      <c r="J462" t="n">
+        <v>350.44</v>
+      </c>
+      <c r="K462" t="n">
+        <v>351.91</v>
+      </c>
+      <c r="L462" t="n">
+        <v>355.52</v>
+      </c>
+      <c r="M462" t="n">
+        <v>362.69</v>
+      </c>
+      <c r="N462" t="n">
+        <v>369.04</v>
+      </c>
+      <c r="O462" t="n">
+        <v>389.95</v>
+      </c>
+      <c r="P462" t="n">
+        <v>400.49</v>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26491,7 +26776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B516"/>
+  <dimension ref="A1:B522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31654,6 +31939,66 @@
       </c>
       <c r="B516" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-01-21 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-01-30 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-02-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-02-15 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>-0.72</v>
       </c>
     </row>
   </sheetData>
@@ -31822,28 +32167,28 @@
         <v>0.153</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2703380441829667</v>
+        <v>-0.2779024065839473</v>
       </c>
       <c r="J2" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K2" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04470896642717315</v>
+        <v>0.04808499121137</v>
       </c>
       <c r="M2" t="n">
-        <v>7.87584848582505</v>
+        <v>7.829247109067109</v>
       </c>
       <c r="N2" t="n">
-        <v>86.48548612282119</v>
+        <v>85.71792464857116</v>
       </c>
       <c r="O2" t="n">
-        <v>9.299757315264801</v>
+        <v>9.258397520552418</v>
       </c>
       <c r="P2" t="n">
-        <v>377.4130722594371</v>
+        <v>377.4908655864148</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31900,28 +32245,28 @@
         <v>0.0901</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08553259476019039</v>
+        <v>-0.08708889795618467</v>
       </c>
       <c r="J3" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K3" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004326161104032389</v>
+        <v>0.004585408193237162</v>
       </c>
       <c r="M3" t="n">
-        <v>8.133241972509083</v>
+        <v>8.06918554939103</v>
       </c>
       <c r="N3" t="n">
-        <v>93.28134299969292</v>
+        <v>92.33767199610922</v>
       </c>
       <c r="O3" t="n">
-        <v>9.658226700574641</v>
+        <v>9.609249294097287</v>
       </c>
       <c r="P3" t="n">
-        <v>379.6614090456495</v>
+        <v>379.6774723740584</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31978,28 +32323,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.340755631998248</v>
+        <v>-0.3295299525751331</v>
       </c>
       <c r="J4" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K4" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05744332322991319</v>
+        <v>0.05495912564129557</v>
       </c>
       <c r="M4" t="n">
-        <v>8.717321536167992</v>
+        <v>8.666938580439306</v>
       </c>
       <c r="N4" t="n">
-        <v>105.5531236910065</v>
+        <v>104.7195821592621</v>
       </c>
       <c r="O4" t="n">
-        <v>10.27390498744302</v>
+        <v>10.23325862857292</v>
       </c>
       <c r="P4" t="n">
-        <v>387.4052081969438</v>
+        <v>387.2898992653861</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32056,28 +32401,28 @@
         <v>0.091</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.30168197399762</v>
+        <v>-0.2863788206642798</v>
       </c>
       <c r="J5" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K5" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05100781286018397</v>
+        <v>0.04695925529379064</v>
       </c>
       <c r="M5" t="n">
-        <v>7.788929358814977</v>
+        <v>7.770090912180043</v>
       </c>
       <c r="N5" t="n">
-        <v>93.70988664479025</v>
+        <v>93.25319605901029</v>
       </c>
       <c r="O5" t="n">
-        <v>9.680386699135022</v>
+        <v>9.656769442158712</v>
       </c>
       <c r="P5" t="n">
-        <v>386.5862787940469</v>
+        <v>386.4290615027841</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32134,28 +32479,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2705371999206607</v>
+        <v>-0.2720582094375529</v>
       </c>
       <c r="J6" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K6" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05416338114333963</v>
+        <v>0.05594509702235451</v>
       </c>
       <c r="M6" t="n">
-        <v>6.554427802545489</v>
+        <v>6.491694697571847</v>
       </c>
       <c r="N6" t="n">
-        <v>70.73349110751744</v>
+        <v>69.97623260366569</v>
       </c>
       <c r="O6" t="n">
-        <v>8.410320511580842</v>
+        <v>8.36517977115051</v>
       </c>
       <c r="P6" t="n">
-        <v>385.0432299756624</v>
+        <v>385.0588720418081</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32212,28 +32557,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02881085201031732</v>
+        <v>-0.05834309441560789</v>
       </c>
       <c r="J7" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K7" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0005163293065125751</v>
+        <v>0.002113239382667054</v>
       </c>
       <c r="M7" t="n">
-        <v>7.079771590374662</v>
+        <v>7.156417472846402</v>
       </c>
       <c r="N7" t="n">
-        <v>88.77442249600784</v>
+        <v>89.89957578946617</v>
       </c>
       <c r="O7" t="n">
-        <v>9.422017963048459</v>
+        <v>9.481538682590825</v>
       </c>
       <c r="P7" t="n">
-        <v>380.8711628138221</v>
+        <v>381.1751841467376</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32290,28 +32635,28 @@
         <v>0.0788</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06518729892536362</v>
+        <v>-0.09609170663342406</v>
       </c>
       <c r="J8" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K8" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002944787729227349</v>
+        <v>0.006342399488031947</v>
       </c>
       <c r="M8" t="n">
-        <v>7.302010444300135</v>
+        <v>7.412525640998226</v>
       </c>
       <c r="N8" t="n">
-        <v>79.62545757559668</v>
+        <v>81.04881032323085</v>
       </c>
       <c r="O8" t="n">
-        <v>8.923309788166982</v>
+        <v>9.002711276234002</v>
       </c>
       <c r="P8" t="n">
-        <v>380.9440210263114</v>
+        <v>381.2615318076689</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32368,28 +32713,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1576593061796221</v>
+        <v>-0.187649731942384</v>
       </c>
       <c r="J9" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K9" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01573413031029469</v>
+        <v>0.02210451120664836</v>
       </c>
       <c r="M9" t="n">
-        <v>7.494272669759</v>
+        <v>7.562473904828539</v>
       </c>
       <c r="N9" t="n">
-        <v>86.05372225136182</v>
+        <v>87.27685518416916</v>
       </c>
       <c r="O9" t="n">
-        <v>9.276514552964482</v>
+        <v>9.342208260586421</v>
       </c>
       <c r="P9" t="n">
-        <v>374.8062262024384</v>
+        <v>375.114358434521</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32446,28 +32791,28 @@
         <v>0.1006</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5466413212376799</v>
+        <v>-0.5656679442204446</v>
       </c>
       <c r="J10" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K10" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1695419397398802</v>
+        <v>0.1811875487511515</v>
       </c>
       <c r="M10" t="n">
-        <v>7.33544787845919</v>
+        <v>7.346648363710863</v>
       </c>
       <c r="N10" t="n">
-        <v>81.00395563485628</v>
+        <v>81.01601754937714</v>
       </c>
       <c r="O10" t="n">
-        <v>9.000219754809118</v>
+        <v>9.000889819866542</v>
       </c>
       <c r="P10" t="n">
-        <v>375.8279296277311</v>
+        <v>376.0234511274527</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32524,28 +32869,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.365225104640941</v>
+        <v>-0.3870945223077374</v>
       </c>
       <c r="J11" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K11" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08163190536192455</v>
+        <v>0.09154826979705599</v>
       </c>
       <c r="M11" t="n">
-        <v>7.374949631178083</v>
+        <v>7.408803762561843</v>
       </c>
       <c r="N11" t="n">
-        <v>83.04985022708713</v>
+        <v>83.30622071733423</v>
       </c>
       <c r="O11" t="n">
-        <v>9.113169055113985</v>
+        <v>9.127224151807285</v>
       </c>
       <c r="P11" t="n">
-        <v>372.6189310314011</v>
+        <v>372.8436449180468</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32602,28 +32947,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6264053253520593</v>
+        <v>-0.6414157316823011</v>
       </c>
       <c r="J12" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K12" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2352593878117935</v>
+        <v>0.2467055576910644</v>
       </c>
       <c r="M12" t="n">
-        <v>6.90159429446634</v>
+        <v>6.900598219272559</v>
       </c>
       <c r="N12" t="n">
-        <v>70.58929257022811</v>
+        <v>70.3812070079934</v>
       </c>
       <c r="O12" t="n">
-        <v>8.401743424446387</v>
+        <v>8.389350809686849</v>
       </c>
       <c r="P12" t="n">
-        <v>378.846460993181</v>
+        <v>379.0007031544377</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32680,28 +33025,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4705539036833158</v>
+        <v>-0.4847892274962959</v>
       </c>
       <c r="J13" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K13" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L13" t="n">
-        <v>0.115923272978304</v>
+        <v>0.1240905387896939</v>
       </c>
       <c r="M13" t="n">
-        <v>7.856270525791495</v>
+        <v>7.833837661639044</v>
       </c>
       <c r="N13" t="n">
-        <v>93.45420345609563</v>
+        <v>92.94330987093078</v>
       </c>
       <c r="O13" t="n">
-        <v>9.667171429952798</v>
+        <v>9.640711066665714</v>
       </c>
       <c r="P13" t="n">
-        <v>380.659851825076</v>
+        <v>380.8061171838503</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32758,28 +33103,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3720997537893597</v>
+        <v>-0.3870228890973359</v>
       </c>
       <c r="J14" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K14" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07832028207519581</v>
+        <v>0.08550023499311221</v>
       </c>
       <c r="M14" t="n">
-        <v>7.991569611026502</v>
+        <v>7.983583758778398</v>
       </c>
       <c r="N14" t="n">
-        <v>90.42727491176051</v>
+        <v>90.00241370335883</v>
       </c>
       <c r="O14" t="n">
-        <v>9.509325681233161</v>
+        <v>9.48696019298905</v>
       </c>
       <c r="P14" t="n">
-        <v>383.4545356288852</v>
+        <v>383.6077810433826</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32836,28 +33181,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2960841730413954</v>
+        <v>-0.2802999560619704</v>
       </c>
       <c r="J15" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K15" t="n">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04505686055494362</v>
+        <v>0.04124349000018745</v>
       </c>
       <c r="M15" t="n">
-        <v>8.230733767453144</v>
+        <v>8.217987685431982</v>
       </c>
       <c r="N15" t="n">
-        <v>103.4809983982151</v>
+        <v>102.9586709283595</v>
       </c>
       <c r="O15" t="n">
-        <v>10.17256105404215</v>
+        <v>10.14685522358329</v>
       </c>
       <c r="P15" t="n">
-        <v>388.623219912908</v>
+        <v>388.4612553980034</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32914,28 +33259,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4521224127388931</v>
+        <v>-0.423697602157546</v>
       </c>
       <c r="J16" t="n">
+        <v>461</v>
+      </c>
+      <c r="K16" t="n">
         <v>456</v>
       </c>
-      <c r="K16" t="n">
-        <v>451</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.07138365902786059</v>
+        <v>0.06381363763092107</v>
       </c>
       <c r="M16" t="n">
-        <v>10.04722291999455</v>
+        <v>10.0756260636908</v>
       </c>
       <c r="N16" t="n">
-        <v>148.214259860967</v>
+        <v>148.5698960274761</v>
       </c>
       <c r="O16" t="n">
-        <v>12.17432790181729</v>
+        <v>12.18892513831618</v>
       </c>
       <c r="P16" t="n">
-        <v>396.8053788888529</v>
+        <v>396.5136009011754</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32973,7 +33318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q457"/>
+  <dimension ref="A1:Q462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72675,6 +73020,441 @@
         </is>
       </c>
     </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-21 22:32:52+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>-45.50397373326016,166.71817046269194</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>-45.503450044353905,166.71870162053847</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>-45.50296931151119,166.71928927719358</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-45.50251493043995,166.71991159551186</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>-45.50211635244189,166.72060730966848</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>-45.50173636139642,166.72131833074835</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>-45.501297246707615,166.72191729693282</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>-45.50082962678075,166.72248625709832</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>-45.50032610170446,166.72302348720942</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>-45.49980789699479,166.72353345778487</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>-45.49927341211217,166.72401096003424</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>-45.49872271135796,166.7244460361323</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>-45.49817168843364,166.7248760708914</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>-45.49752884528156,166.7251263276177</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>-45.49695134858242,166.72551170000588</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:27:12+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>-45.5039963989505,166.7182002718486</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>-45.503476136150915,166.7187359356076</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>-45.50297919472466,166.71930227529455</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-45.50251565520551,166.71991254870463</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-45.50211931737555,166.72061120909672</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>-45.50175156822021,166.72133911173196</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>-45.5013086042609,166.72193572429143</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>-45.500842665008975,166.7225104765158</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>-45.500337339603576,166.7230443624308</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>-45.49981962579959,166.72355524492332</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>-45.499289700843356,166.7240416041048</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>-45.498738551038926,166.72447746681223</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>-45.49818338550559,166.7249002548518</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>-45.49752884528156,166.7251263276177</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>-45.496938176757226,166.72548446724434</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-14 22:33:20+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>-45.50400325136719,166.71820928392393</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>-45.50348766661397,166.71875110010532</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>-45.50298505876407,166.71930998750327</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-45.502517104736604,166.71991445509028</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>-45.50212379771952,166.7206171015669</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>-45.50175357422649,166.72134185305404</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>-45.50130724372081,166.72193351684706</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>-45.50084255590248,166.7225102738428</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>-45.500343122210545,166.7230551040529</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>-45.499824099110214,166.72356355443904</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>-45.49929316422713,166.7240481197899</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>-45.49873985794295,166.72448006010347</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>-45.49817855410687,166.72489026582343</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>-45.49752818414436,166.7251249607119</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>-45.49693553222019,166.72547899966443</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-15 22:26:59+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>-45.504003976142016,166.71821023712434</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>-45.503492410575426,166.71875733921476</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>-45.50298446577133,166.71930920761693</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-45.50251585286883,166.71991280866632</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>-45.50212860750027,166.72062342730797</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>-45.501751244670785,166.72133866958325</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>-45.501303398715976,166.7219272784178</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>-45.50083922815428,166.72250409231677</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>-45.50034601351368,166.7230604748648</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>-45.49982573568713,166.7235665945061</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>-45.49929316422713,166.7240481197899</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>-45.4987368782017,166.72447414739963</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>-45.4981716375768,166.72487596574376</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>-45.49752294590297,166.72511413061326</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>-45.496932480831,166.72547269091908</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>-45.50400674346394,166.718213876617</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>-45.503492937682246,166.7187580324492</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>-45.50298953915342,166.71931587997844</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>-45.5025168411855,166.7199141084747</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>-45.50212425893138,166.72061770814474</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>-45.5017449031021,166.7213300034697</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>-45.501300559327596,166.7219226715783</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>-45.50083917360103,166.7225039909803</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>-45.50035141424913,166.7230705071376</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>-45.49982393545251,166.72356325043236</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>-45.499285371613205,166.72403345949954</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>-45.49872673662414,166.72445402346509</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>-45.4981604999257,166.72485293841726</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>-45.49751724995013,166.7251023541977</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>-45.496926734047186,166.72546080945057</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0491/nzd0491.xlsx
+++ b/data/nzd0491/nzd0491.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q462"/>
+  <dimension ref="A1:Q464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26762,6 +26762,120 @@
       <c r="Q462" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:33:16+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>366.03</v>
+      </c>
+      <c r="C463" t="n">
+        <v>375.77</v>
+      </c>
+      <c r="D463" t="n">
+        <v>384.09</v>
+      </c>
+      <c r="E463" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="F463" t="n">
+        <v>377.56</v>
+      </c>
+      <c r="G463" t="n">
+        <v>367.78</v>
+      </c>
+      <c r="H463" t="n">
+        <v>366.29</v>
+      </c>
+      <c r="I463" t="n">
+        <v>357.56</v>
+      </c>
+      <c r="J463" t="n">
+        <v>351.8</v>
+      </c>
+      <c r="K463" t="n">
+        <v>353.22</v>
+      </c>
+      <c r="L463" t="n">
+        <v>356.83</v>
+      </c>
+      <c r="M463" t="n">
+        <v>363.85</v>
+      </c>
+      <c r="N463" t="n">
+        <v>370.66</v>
+      </c>
+      <c r="O463" t="n">
+        <v>390.99</v>
+      </c>
+      <c r="P463" t="n">
+        <v>400.91</v>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:54+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>365.3</v>
+      </c>
+      <c r="C464" t="n">
+        <v>375.81</v>
+      </c>
+      <c r="D464" t="n">
+        <v>383.93</v>
+      </c>
+      <c r="E464" t="n">
+        <v>386</v>
+      </c>
+      <c r="F464" t="n">
+        <v>376.78</v>
+      </c>
+      <c r="G464" t="n">
+        <v>368.66</v>
+      </c>
+      <c r="H464" t="n">
+        <v>366.56</v>
+      </c>
+      <c r="I464" t="n">
+        <v>357.48</v>
+      </c>
+      <c r="J464" t="n">
+        <v>351.5</v>
+      </c>
+      <c r="K464" t="n">
+        <v>353.92</v>
+      </c>
+      <c r="L464" t="n">
+        <v>357.56</v>
+      </c>
+      <c r="M464" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="N464" t="n">
+        <v>371.13</v>
+      </c>
+      <c r="O464" t="n">
+        <v>391.58</v>
+      </c>
+      <c r="P464" t="n">
+        <v>401.24</v>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26776,7 +26890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B522"/>
+  <dimension ref="A1:B524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31999,6 +32113,26 @@
       </c>
       <c r="B522" t="n">
         <v>-0.72</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>0.73</v>
       </c>
     </row>
   </sheetData>
@@ -32167,28 +32301,28 @@
         <v>0.153</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2779024065839473</v>
+        <v>-0.2816494239124815</v>
       </c>
       <c r="J2" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K2" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04808499121137</v>
+        <v>0.04970478691444868</v>
       </c>
       <c r="M2" t="n">
-        <v>7.829247109067109</v>
+        <v>7.814763383693668</v>
       </c>
       <c r="N2" t="n">
-        <v>85.71792464857116</v>
+        <v>85.43422354951329</v>
       </c>
       <c r="O2" t="n">
-        <v>9.258397520552418</v>
+        <v>9.243063537026741</v>
       </c>
       <c r="P2" t="n">
-        <v>377.4908655864148</v>
+        <v>377.5294753030008</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32245,28 +32379,28 @@
         <v>0.0901</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08708889795618467</v>
+        <v>-0.08841625903632906</v>
       </c>
       <c r="J3" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K3" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004585408193237162</v>
+        <v>0.004767876786303082</v>
       </c>
       <c r="M3" t="n">
-        <v>8.06918554939103</v>
+        <v>8.041139767367412</v>
       </c>
       <c r="N3" t="n">
-        <v>92.33767199610922</v>
+        <v>91.94883880648698</v>
       </c>
       <c r="O3" t="n">
-        <v>9.609249294097287</v>
+        <v>9.588995714176066</v>
       </c>
       <c r="P3" t="n">
-        <v>379.6774723740584</v>
+        <v>379.691146551229</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32323,28 +32457,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3295299525751331</v>
+        <v>-0.3250463912172273</v>
       </c>
       <c r="J4" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K4" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05495912564129557</v>
+        <v>0.05395406606836628</v>
       </c>
       <c r="M4" t="n">
-        <v>8.666938580439306</v>
+        <v>8.646957609840252</v>
       </c>
       <c r="N4" t="n">
-        <v>104.7195821592621</v>
+        <v>104.3905913070855</v>
       </c>
       <c r="O4" t="n">
-        <v>10.23325862857292</v>
+        <v>10.21717139462217</v>
       </c>
       <c r="P4" t="n">
-        <v>387.2898992653861</v>
+        <v>387.2437106277391</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32401,28 +32535,28 @@
         <v>0.091</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2863788206642798</v>
+        <v>-0.2803044941148928</v>
       </c>
       <c r="J5" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K5" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04695925529379064</v>
+        <v>0.04536334565485567</v>
       </c>
       <c r="M5" t="n">
-        <v>7.770090912180043</v>
+        <v>7.762672599131774</v>
       </c>
       <c r="N5" t="n">
-        <v>93.25319605901029</v>
+        <v>93.0782565758925</v>
       </c>
       <c r="O5" t="n">
-        <v>9.656769442158712</v>
+        <v>9.647707322254988</v>
       </c>
       <c r="P5" t="n">
-        <v>386.4290615027841</v>
+        <v>386.3664918687021</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32479,28 +32613,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2720582094375529</v>
+        <v>-0.2726612887431987</v>
       </c>
       <c r="J6" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K6" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05594509702235451</v>
+        <v>0.05666063891823547</v>
       </c>
       <c r="M6" t="n">
-        <v>6.491694697571847</v>
+        <v>6.466614704712512</v>
       </c>
       <c r="N6" t="n">
-        <v>69.97623260366569</v>
+        <v>69.67685580124741</v>
       </c>
       <c r="O6" t="n">
-        <v>8.36517977115051</v>
+        <v>8.347266366975923</v>
       </c>
       <c r="P6" t="n">
-        <v>385.0588720418081</v>
+        <v>385.0650843857204</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32557,28 +32691,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.05834309441560789</v>
+        <v>-0.06785119792784065</v>
       </c>
       <c r="J7" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K7" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002113239382667054</v>
+        <v>0.002864194755750393</v>
       </c>
       <c r="M7" t="n">
-        <v>7.156417472846402</v>
+        <v>7.175485694414395</v>
       </c>
       <c r="N7" t="n">
-        <v>89.89957578946617</v>
+        <v>90.06827140254637</v>
       </c>
       <c r="O7" t="n">
-        <v>9.481538682590825</v>
+        <v>9.490430517239266</v>
       </c>
       <c r="P7" t="n">
-        <v>381.1751841467376</v>
+        <v>381.2733167035803</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32635,28 +32769,28 @@
         <v>0.0788</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09609170663342406</v>
+        <v>-0.1063168275838969</v>
       </c>
       <c r="J8" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K8" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006342399488031947</v>
+        <v>0.00776156776812198</v>
       </c>
       <c r="M8" t="n">
-        <v>7.412525640998226</v>
+        <v>7.44396598751764</v>
       </c>
       <c r="N8" t="n">
-        <v>81.04881032323085</v>
+        <v>81.34403267857103</v>
       </c>
       <c r="O8" t="n">
-        <v>9.002711276234002</v>
+        <v>9.019092674907551</v>
       </c>
       <c r="P8" t="n">
-        <v>381.2615318076689</v>
+        <v>381.3668575132608</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32713,28 +32847,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.187649731942384</v>
+        <v>-0.1981673424584821</v>
       </c>
       <c r="J9" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K9" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02210451120664836</v>
+        <v>0.02461931016907604</v>
       </c>
       <c r="M9" t="n">
-        <v>7.562473904828539</v>
+        <v>7.582699192330494</v>
       </c>
       <c r="N9" t="n">
-        <v>87.27685518416916</v>
+        <v>87.58253959955559</v>
       </c>
       <c r="O9" t="n">
-        <v>9.342208260586421</v>
+        <v>9.3585543541487</v>
       </c>
       <c r="P9" t="n">
-        <v>375.114358434521</v>
+        <v>375.2226970810825</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32791,28 +32925,28 @@
         <v>0.1006</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5656679442204446</v>
+        <v>-0.5735461771185349</v>
       </c>
       <c r="J10" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K10" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1811875487511515</v>
+        <v>0.1859841985606386</v>
       </c>
       <c r="M10" t="n">
-        <v>7.346648363710863</v>
+        <v>7.352888131508407</v>
       </c>
       <c r="N10" t="n">
-        <v>81.01601754937714</v>
+        <v>81.04918584261273</v>
       </c>
       <c r="O10" t="n">
-        <v>9.000889819866542</v>
+        <v>9.002732132114824</v>
       </c>
       <c r="P10" t="n">
-        <v>376.0234511274527</v>
+        <v>376.1046024262434</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32869,28 +33003,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3870945223077374</v>
+        <v>-0.3946385645838167</v>
       </c>
       <c r="J11" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K11" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09154826979705599</v>
+        <v>0.0952266842497862</v>
       </c>
       <c r="M11" t="n">
-        <v>7.408803762561843</v>
+        <v>7.416147978355905</v>
       </c>
       <c r="N11" t="n">
-        <v>83.30622071733423</v>
+        <v>83.29813091486207</v>
       </c>
       <c r="O11" t="n">
-        <v>9.127224151807285</v>
+        <v>9.12678097221918</v>
       </c>
       <c r="P11" t="n">
-        <v>372.8436449180468</v>
+        <v>372.9213535527325</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32947,28 +33081,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6414157316823011</v>
+        <v>-0.6455022710048747</v>
       </c>
       <c r="J12" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K12" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2467055576910644</v>
+        <v>0.2504982944833659</v>
       </c>
       <c r="M12" t="n">
-        <v>6.900598219272559</v>
+        <v>6.891271623924123</v>
       </c>
       <c r="N12" t="n">
-        <v>70.3812070079934</v>
+        <v>70.18082856912868</v>
       </c>
       <c r="O12" t="n">
-        <v>8.389350809686849</v>
+        <v>8.377399869239182</v>
       </c>
       <c r="P12" t="n">
-        <v>379.0007031544377</v>
+        <v>379.0427971208622</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33025,28 +33159,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4847892274962959</v>
+        <v>-0.4882155689815986</v>
       </c>
       <c r="J13" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K13" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1240905387896939</v>
+        <v>0.1265439416583191</v>
       </c>
       <c r="M13" t="n">
-        <v>7.833837661639044</v>
+        <v>7.815034977372819</v>
       </c>
       <c r="N13" t="n">
-        <v>92.94330987093078</v>
+        <v>92.61429883315469</v>
       </c>
       <c r="O13" t="n">
-        <v>9.640711066665714</v>
+        <v>9.623632309744314</v>
       </c>
       <c r="P13" t="n">
-        <v>380.8061171838503</v>
+        <v>380.8414108211113</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33103,28 +33237,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3870228890973359</v>
+        <v>-0.3891179753239893</v>
       </c>
       <c r="J14" t="n">
+        <v>463</v>
+      </c>
+      <c r="K14" t="n">
         <v>461</v>
       </c>
-      <c r="K14" t="n">
-        <v>459</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.08550023499311221</v>
+        <v>0.08704150766102925</v>
       </c>
       <c r="M14" t="n">
-        <v>7.983583758778398</v>
+        <v>7.95998788866843</v>
       </c>
       <c r="N14" t="n">
-        <v>90.00241370335883</v>
+        <v>89.63940173821497</v>
       </c>
       <c r="O14" t="n">
-        <v>9.48696019298905</v>
+        <v>9.467808708366206</v>
       </c>
       <c r="P14" t="n">
-        <v>383.6077810433826</v>
+        <v>383.6293545770239</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33181,28 +33315,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2802999560619704</v>
+        <v>-0.271826901080344</v>
       </c>
       <c r="J15" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K15" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04124349000018745</v>
+        <v>0.03905866892668586</v>
       </c>
       <c r="M15" t="n">
-        <v>8.217987685431982</v>
+        <v>8.224520889666694</v>
       </c>
       <c r="N15" t="n">
-        <v>102.9586709283595</v>
+        <v>102.9579449188537</v>
       </c>
       <c r="O15" t="n">
-        <v>10.14685522358329</v>
+        <v>10.14681944842095</v>
       </c>
       <c r="P15" t="n">
-        <v>388.4612553980034</v>
+        <v>388.3740913723151</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33259,28 +33393,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.423697602157546</v>
+        <v>-0.4106431501133824</v>
       </c>
       <c r="J16" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K16" t="n">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06381363763092107</v>
+        <v>0.06028055571132018</v>
       </c>
       <c r="M16" t="n">
-        <v>10.0756260636908</v>
+        <v>10.09466367584587</v>
       </c>
       <c r="N16" t="n">
-        <v>148.5698960274761</v>
+        <v>148.9853579191951</v>
       </c>
       <c r="O16" t="n">
-        <v>12.18892513831618</v>
+        <v>12.20595583799954</v>
       </c>
       <c r="P16" t="n">
-        <v>396.5136009011754</v>
+        <v>396.3792632504161</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33318,7 +33452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q462"/>
+  <dimension ref="A1:Q464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73455,6 +73589,180 @@
         </is>
       </c>
     </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:33:16+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>-45.5040012747086,166.7182066842866</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>-45.503485821740014,166.71874867378526</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>-45.502979721829355,166.71930296852673</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-45.50251321735769,166.71990934251082</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>-45.50212017391191,166.7206123355983</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>-45.501736296686516,166.72131824231866</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>-45.501292691854786,166.72190990679633</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>-45.500832027124375,166.72249071590235</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>-45.5003439950568,166.72305672543004</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>-45.49981678906574,166.72354997547504</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>-45.49927828249767,166.72402012271124</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>-45.49872067258657,166.72444199060055</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>-45.49815226111261,166.72483590451054</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>-45.49751196085007,166.72509141895688</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>-45.49692459807415,166.72545639333015</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:54+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>-45.50400608457779,166.71821301007108</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>-45.503485558186576,166.71874832716813</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>-45.502980776038704,166.71930435499112</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-45.50251585286883,166.71991280866632</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>-45.50212531312992,166.72061909460848</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>-45.50173060221552,166.72131046050643</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>-45.501291094698516,166.72190731545004</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>-45.50083246355045,166.722491526594</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>-45.50034563164347,166.72305976551226</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>-45.49981297038522,166.7235428819878</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>-45.499274332073924,166.724012690762</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>-45.49871994071988,166.7244405383585</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>-45.49814987083924,166.7248309625756</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>-45.497508960302504,166.7250852153116</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>-45.49692291980952,166.7254529235215</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0491/nzd0491.xlsx
+++ b/data/nzd0491/nzd0491.xlsx
@@ -26890,7 +26890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B524"/>
+  <dimension ref="A1:B525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32133,6 +32133,16 @@
       </c>
       <c r="B524" t="n">
         <v>0.73</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0491/nzd0491.xlsx
+++ b/data/nzd0491/nzd0491.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q464"/>
+  <dimension ref="A1:Q466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26876,6 +26876,120 @@
       <c r="Q464" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:26:53+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>370.23</v>
+      </c>
+      <c r="C465" t="n">
+        <v>373.54</v>
+      </c>
+      <c r="D465" t="n">
+        <v>382.66</v>
+      </c>
+      <c r="E465" t="n">
+        <v>385.56</v>
+      </c>
+      <c r="F465" t="n">
+        <v>384.06</v>
+      </c>
+      <c r="G465" t="n">
+        <v>378.54</v>
+      </c>
+      <c r="H465" t="n">
+        <v>366.31</v>
+      </c>
+      <c r="I465" t="n">
+        <v>376.11</v>
+      </c>
+      <c r="J465" t="n">
+        <v>365.63</v>
+      </c>
+      <c r="K465" t="n">
+        <v>353.13</v>
+      </c>
+      <c r="L465" t="n">
+        <v>356.94</v>
+      </c>
+      <c r="M465" t="n">
+        <v>363.2</v>
+      </c>
+      <c r="N465" t="n">
+        <v>370.19</v>
+      </c>
+      <c r="O465" t="n">
+        <v>391.35</v>
+      </c>
+      <c r="P465" t="n">
+        <v>401.43</v>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-12 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>370.23</v>
+      </c>
+      <c r="C466" t="n">
+        <v>385.92</v>
+      </c>
+      <c r="D466" t="n">
+        <v>391.36</v>
+      </c>
+      <c r="E466" t="n">
+        <v>395.78</v>
+      </c>
+      <c r="F466" t="n">
+        <v>384.06</v>
+      </c>
+      <c r="G466" t="n">
+        <v>378.54</v>
+      </c>
+      <c r="H466" t="n">
+        <v>366.31</v>
+      </c>
+      <c r="I466" t="n">
+        <v>392.06</v>
+      </c>
+      <c r="J466" t="n">
+        <v>365.63</v>
+      </c>
+      <c r="K466" t="n">
+        <v>353.13</v>
+      </c>
+      <c r="L466" t="n">
+        <v>356.94</v>
+      </c>
+      <c r="M466" t="n">
+        <v>363.2</v>
+      </c>
+      <c r="N466" t="n">
+        <v>370.19</v>
+      </c>
+      <c r="O466" t="n">
+        <v>391.35</v>
+      </c>
+      <c r="P466" t="n">
+        <v>401.43</v>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26890,7 +27004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B525"/>
+  <dimension ref="A1:B526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32143,6 +32257,16 @@
       </c>
       <c r="B525" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-04-12 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -32311,28 +32435,28 @@
         <v>0.153</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2816494239124815</v>
+        <v>-0.2815335013404183</v>
       </c>
       <c r="J2" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K2" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04970478691444868</v>
+        <v>0.05009519495137016</v>
       </c>
       <c r="M2" t="n">
-        <v>7.814763383693668</v>
+        <v>7.781678553738891</v>
       </c>
       <c r="N2" t="n">
-        <v>85.43422354951329</v>
+        <v>85.06605631395152</v>
       </c>
       <c r="O2" t="n">
-        <v>9.243063537026741</v>
+        <v>9.223126168168335</v>
       </c>
       <c r="P2" t="n">
-        <v>377.5294753030008</v>
+        <v>377.5282758496495</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32389,28 +32513,28 @@
         <v>0.0901</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08841625903632906</v>
+        <v>-0.08644519637108881</v>
       </c>
       <c r="J3" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K3" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004767876786303082</v>
+        <v>0.004590470894784482</v>
       </c>
       <c r="M3" t="n">
-        <v>8.041139767367412</v>
+        <v>8.033291274756241</v>
       </c>
       <c r="N3" t="n">
-        <v>91.94883880648698</v>
+        <v>91.74176010218325</v>
       </c>
       <c r="O3" t="n">
-        <v>9.588995714176066</v>
+        <v>9.578191901511644</v>
       </c>
       <c r="P3" t="n">
-        <v>379.691146551229</v>
+        <v>379.6707034897358</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32467,28 +32591,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3250463912172273</v>
+        <v>-0.3181293415956258</v>
       </c>
       <c r="J4" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K4" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05395406606836628</v>
+        <v>0.05206675788967263</v>
       </c>
       <c r="M4" t="n">
-        <v>8.646957609840252</v>
+        <v>8.636864004785243</v>
       </c>
       <c r="N4" t="n">
-        <v>104.3905913070855</v>
+        <v>104.3194894131988</v>
       </c>
       <c r="O4" t="n">
-        <v>10.21717139462217</v>
+        <v>10.2136912726594</v>
       </c>
       <c r="P4" t="n">
-        <v>387.2437106277391</v>
+        <v>387.1721208687022</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32545,28 +32669,28 @@
         <v>0.091</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2803044941148928</v>
+        <v>-0.2706128817441038</v>
       </c>
       <c r="J5" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K5" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04536334565485567</v>
+        <v>0.04247641357622201</v>
       </c>
       <c r="M5" t="n">
-        <v>7.762672599131774</v>
+        <v>7.770683106114359</v>
       </c>
       <c r="N5" t="n">
-        <v>93.0782565758925</v>
+        <v>93.37269471524175</v>
       </c>
       <c r="O5" t="n">
-        <v>9.647707322254988</v>
+        <v>9.662954761109138</v>
       </c>
       <c r="P5" t="n">
-        <v>386.3664918687021</v>
+        <v>386.2662067380584</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32623,28 +32747,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2726612887431987</v>
+        <v>-0.2675390203944811</v>
       </c>
       <c r="J6" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K6" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05666063891823547</v>
+        <v>0.05501549779518911</v>
       </c>
       <c r="M6" t="n">
-        <v>6.466614704712512</v>
+        <v>6.466561052488833</v>
       </c>
       <c r="N6" t="n">
-        <v>69.67685580124741</v>
+        <v>69.54008622002311</v>
       </c>
       <c r="O6" t="n">
-        <v>8.347266366975923</v>
+        <v>8.339069865400043</v>
       </c>
       <c r="P6" t="n">
-        <v>385.0650843857204</v>
+        <v>385.0121044742915</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32701,28 +32825,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06785119792784065</v>
+        <v>-0.06863168168058516</v>
       </c>
       <c r="J7" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K7" t="n">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002864194755750393</v>
+        <v>0.002956759175434809</v>
       </c>
       <c r="M7" t="n">
-        <v>7.175485694414395</v>
+        <v>7.148656648818556</v>
       </c>
       <c r="N7" t="n">
-        <v>90.06827140254637</v>
+        <v>89.68382237048871</v>
       </c>
       <c r="O7" t="n">
-        <v>9.490430517239266</v>
+        <v>9.470154294967358</v>
       </c>
       <c r="P7" t="n">
-        <v>381.2733167035803</v>
+        <v>381.2814051711675</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32779,28 +32903,28 @@
         <v>0.0788</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1063168275838969</v>
+        <v>-0.1164440705494926</v>
       </c>
       <c r="J8" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K8" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00776156776812198</v>
+        <v>0.009307644797326375</v>
       </c>
       <c r="M8" t="n">
-        <v>7.44396598751764</v>
+        <v>7.474157025712743</v>
       </c>
       <c r="N8" t="n">
-        <v>81.34403267857103</v>
+        <v>81.63099469031881</v>
       </c>
       <c r="O8" t="n">
-        <v>9.019092674907551</v>
+        <v>9.034987254574231</v>
       </c>
       <c r="P8" t="n">
-        <v>381.3668575132608</v>
+        <v>381.4716040379233</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32857,28 +32981,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1981673424584821</v>
+        <v>-0.1865010508801631</v>
       </c>
       <c r="J9" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K9" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02461931016907604</v>
+        <v>0.02178928642184119</v>
       </c>
       <c r="M9" t="n">
-        <v>7.582699192330494</v>
+        <v>7.611879229128529</v>
       </c>
       <c r="N9" t="n">
-        <v>87.58253959955559</v>
+        <v>88.3228947235788</v>
       </c>
       <c r="O9" t="n">
-        <v>9.3585543541487</v>
+        <v>9.398026107836623</v>
       </c>
       <c r="P9" t="n">
-        <v>375.2226970810825</v>
+        <v>375.1019629372263</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32935,28 +33059,28 @@
         <v>0.1006</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5735461771185349</v>
+        <v>-0.5696812583289584</v>
       </c>
       <c r="J10" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K10" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1859841985606386</v>
+        <v>0.1851373501425145</v>
       </c>
       <c r="M10" t="n">
-        <v>7.352888131508407</v>
+        <v>7.342562248388093</v>
       </c>
       <c r="N10" t="n">
-        <v>81.04918584261273</v>
+        <v>80.79333829560626</v>
       </c>
       <c r="O10" t="n">
-        <v>9.002732132114824</v>
+        <v>8.988511461616225</v>
       </c>
       <c r="P10" t="n">
-        <v>376.1046024262434</v>
+        <v>376.0646272826585</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33013,28 +33137,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3946385645838167</v>
+        <v>-0.4023829556693571</v>
       </c>
       <c r="J11" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K11" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0952266842497862</v>
+        <v>0.09903720756422851</v>
       </c>
       <c r="M11" t="n">
-        <v>7.416147978355905</v>
+        <v>7.424122272387859</v>
       </c>
       <c r="N11" t="n">
-        <v>83.29813091486207</v>
+        <v>83.31226520030152</v>
       </c>
       <c r="O11" t="n">
-        <v>9.12678097221918</v>
+        <v>9.127555269638279</v>
       </c>
       <c r="P11" t="n">
-        <v>372.9213535527325</v>
+        <v>373.0014540748934</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33091,28 +33215,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6455022710048747</v>
+        <v>-0.6496805990873478</v>
       </c>
       <c r="J12" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K12" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2504982944833659</v>
+        <v>0.2543520311676395</v>
       </c>
       <c r="M12" t="n">
-        <v>6.891271623924123</v>
+        <v>6.882305108812364</v>
       </c>
       <c r="N12" t="n">
-        <v>70.18082856912868</v>
+        <v>69.98738155250851</v>
       </c>
       <c r="O12" t="n">
-        <v>8.377399869239182</v>
+        <v>8.365846134881307</v>
       </c>
       <c r="P12" t="n">
-        <v>379.0427971208622</v>
+        <v>379.0860136399741</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33169,28 +33293,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4882155689815986</v>
+        <v>-0.4921381636856249</v>
       </c>
       <c r="J13" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K13" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1265439416583191</v>
+        <v>0.1292247447807257</v>
       </c>
       <c r="M13" t="n">
-        <v>7.815034977372819</v>
+        <v>7.798754459826018</v>
       </c>
       <c r="N13" t="n">
-        <v>92.61429883315469</v>
+        <v>92.31149946825531</v>
       </c>
       <c r="O13" t="n">
-        <v>9.623632309744314</v>
+        <v>9.607887357179793</v>
       </c>
       <c r="P13" t="n">
-        <v>380.8414108211113</v>
+        <v>380.8819823078512</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33247,28 +33371,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3891179753239893</v>
+        <v>-0.3917268504311812</v>
       </c>
       <c r="J14" t="n">
+        <v>465</v>
+      </c>
+      <c r="K14" t="n">
         <v>463</v>
       </c>
-      <c r="K14" t="n">
-        <v>461</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.08704150766102925</v>
+        <v>0.08880071140063972</v>
       </c>
       <c r="M14" t="n">
-        <v>7.95998788866843</v>
+        <v>7.939237956452233</v>
       </c>
       <c r="N14" t="n">
-        <v>89.63940173821497</v>
+        <v>89.29465098317063</v>
       </c>
       <c r="O14" t="n">
-        <v>9.467808708366206</v>
+        <v>9.449584698978608</v>
       </c>
       <c r="P14" t="n">
-        <v>383.6293545770239</v>
+        <v>383.6563300004973</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33325,28 +33449,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.271826901080344</v>
+        <v>-0.2634327312138645</v>
       </c>
       <c r="J15" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K15" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03905866892668586</v>
+        <v>0.03693889184745813</v>
       </c>
       <c r="M15" t="n">
-        <v>8.224520889666694</v>
+        <v>8.23049891381652</v>
       </c>
       <c r="N15" t="n">
-        <v>102.9579449188537</v>
+        <v>102.9531520650241</v>
       </c>
       <c r="O15" t="n">
-        <v>10.14681944842095</v>
+        <v>10.1465832704918</v>
       </c>
       <c r="P15" t="n">
-        <v>388.3740913723151</v>
+        <v>388.2873788970368</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33403,28 +33527,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4106431501133824</v>
+        <v>-0.3975024865313092</v>
       </c>
       <c r="J16" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K16" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06028055571132018</v>
+        <v>0.05679256794996146</v>
       </c>
       <c r="M16" t="n">
-        <v>10.09466367584587</v>
+        <v>10.11340197515838</v>
       </c>
       <c r="N16" t="n">
-        <v>148.9853579191951</v>
+        <v>149.422303572836</v>
       </c>
       <c r="O16" t="n">
-        <v>12.20595583799954</v>
+        <v>12.22384160453807</v>
       </c>
       <c r="P16" t="n">
-        <v>396.3792632504161</v>
+        <v>396.243472977157</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33462,7 +33586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q464"/>
+  <dimension ref="A1:Q466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73773,6 +73897,180 @@
         </is>
       </c>
     </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:26:53+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>-45.503973601482876,166.71817028938298</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>-45.503500514842244,166.7187679976958</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>-45.502989143824955,166.71931536005414</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-45.502518751931,166.71991662143773</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>-45.50207734708199,166.7205560105613</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>-45.501666668805356,166.7212230920862</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>-45.50129257354692,166.72190971484474</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>-45.50073083068485,166.72230273711537</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>-45.500268548332755,166.7229165778354</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>-45.499817280038926,166.7235508874949</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>-45.49927768722838,166.7240190028284</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>-45.4987240705388,166.72444873315362</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>-45.498154651385775,166.7248408464459</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>-45.49751013000752,166.7250876336817</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>-45.4969219535359,166.72545092575297</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-12 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>-45.503973601482876,166.71817028938298</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>-45.5034189450289,166.71866071979042</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>-45.50293182117667,166.71923997110522</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>-45.502451414595605,166.7198280612572</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>-45.50207734708199,166.7205560105613</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>-45.501666668805356,166.7212230920862</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>-45.50129257354692,166.72190971484474</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>-45.500643817892104,166.72214110631222</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>-45.500268548332755,166.7229165778354</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>-45.499817280038926,166.7235508874949</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>-45.49927768722838,166.7240190028284</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>-45.4987240705388,166.72444873315362</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>-45.498154651385775,166.7248408464459</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>-45.49751013000752,166.7250876336817</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>-45.4969219535359,166.72545092575297</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0491/nzd0491.xlsx
+++ b/data/nzd0491/nzd0491.xlsx
@@ -26882,110 +26882,110 @@
     <row r="465">
       <c r="A465" s="1" t="inlineStr">
         <is>
-          <t>2026-03-27 22:26:53+00:00</t>
+          <t>2026-04-20 22:26:29+00:00</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>370.23</v>
+        <v>364.74</v>
       </c>
       <c r="C465" t="n">
-        <v>373.54</v>
+        <v>373.71</v>
       </c>
       <c r="D465" t="n">
-        <v>382.66</v>
+        <v>382.46</v>
       </c>
       <c r="E465" t="n">
-        <v>385.56</v>
+        <v>387.36</v>
       </c>
       <c r="F465" t="n">
-        <v>384.06</v>
+        <v>378.26</v>
       </c>
       <c r="G465" t="n">
-        <v>378.54</v>
+        <v>369.47</v>
       </c>
       <c r="H465" t="n">
-        <v>366.31</v>
+        <v>366.21</v>
       </c>
       <c r="I465" t="n">
-        <v>376.11</v>
+        <v>358.16</v>
       </c>
       <c r="J465" t="n">
-        <v>365.63</v>
+        <v>352.38</v>
       </c>
       <c r="K465" t="n">
-        <v>353.13</v>
+        <v>355.04</v>
       </c>
       <c r="L465" t="n">
-        <v>356.94</v>
+        <v>358.07</v>
       </c>
       <c r="M465" t="n">
-        <v>363.2</v>
+        <v>364.64</v>
       </c>
       <c r="N465" t="n">
-        <v>370.19</v>
+        <v>371.24</v>
       </c>
       <c r="O465" t="n">
-        <v>391.35</v>
+        <v>391.85</v>
       </c>
       <c r="P465" t="n">
-        <v>401.43</v>
+        <v>401.81</v>
       </c>
       <c r="Q465" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L8</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="1" t="inlineStr">
         <is>
-          <t>2026-04-12 22:26:45+00:00</t>
+          <t>2026-05-14 22:26:25+00:00</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>370.23</v>
+        <v>365.28</v>
       </c>
       <c r="C466" t="n">
-        <v>385.92</v>
+        <v>374.13</v>
       </c>
       <c r="D466" t="n">
-        <v>391.36</v>
+        <v>381.43</v>
       </c>
       <c r="E466" t="n">
-        <v>395.78</v>
+        <v>387.06</v>
       </c>
       <c r="F466" t="n">
-        <v>384.06</v>
+        <v>377.78</v>
       </c>
       <c r="G466" t="n">
-        <v>378.54</v>
+        <v>368.89</v>
       </c>
       <c r="H466" t="n">
-        <v>366.31</v>
+        <v>366.35</v>
       </c>
       <c r="I466" t="n">
-        <v>392.06</v>
+        <v>358.92</v>
       </c>
       <c r="J466" t="n">
-        <v>365.63</v>
+        <v>354.12</v>
       </c>
       <c r="K466" t="n">
-        <v>353.13</v>
+        <v>357.06</v>
       </c>
       <c r="L466" t="n">
-        <v>356.94</v>
+        <v>358.8</v>
       </c>
       <c r="M466" t="n">
-        <v>363.2</v>
+        <v>365.73</v>
       </c>
       <c r="N466" t="n">
-        <v>370.19</v>
+        <v>372.14</v>
       </c>
       <c r="O466" t="n">
-        <v>391.35</v>
+        <v>392.84</v>
       </c>
       <c r="P466" t="n">
-        <v>401.43</v>
+        <v>402.68</v>
       </c>
       <c r="Q466" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B526"/>
+  <dimension ref="A1:B529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32267,6 +32267,36 @@
       </c>
       <c r="B526" t="n">
         <v>0.13</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-05-22 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>-0.72</v>
       </c>
     </row>
   </sheetData>
@@ -32435,7 +32465,7 @@
         <v>0.153</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2815335013404183</v>
+        <v>-0.2858584131027693</v>
       </c>
       <c r="J2" t="n">
         <v>465</v>
@@ -32444,19 +32474,19 @@
         <v>464</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05009519495137016</v>
+        <v>0.05150981522444886</v>
       </c>
       <c r="M2" t="n">
-        <v>7.781678553738891</v>
+        <v>7.802454771234358</v>
       </c>
       <c r="N2" t="n">
-        <v>85.06605631395152</v>
+        <v>85.17501144761505</v>
       </c>
       <c r="O2" t="n">
-        <v>9.223126168168335</v>
+        <v>9.229030905117559</v>
       </c>
       <c r="P2" t="n">
-        <v>377.5282758496495</v>
+        <v>377.5731719928133</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32513,7 +32543,7 @@
         <v>0.0901</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08644519637108881</v>
+        <v>-0.091269917308515</v>
       </c>
       <c r="J3" t="n">
         <v>465</v>
@@ -32522,19 +32552,19 @@
         <v>464</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004590470894784482</v>
+        <v>0.005122861715456173</v>
       </c>
       <c r="M3" t="n">
-        <v>8.033291274756241</v>
+        <v>8.021057997321327</v>
       </c>
       <c r="N3" t="n">
-        <v>91.74176010218325</v>
+        <v>91.60267936784395</v>
       </c>
       <c r="O3" t="n">
-        <v>9.578191901511644</v>
+        <v>9.570928866512588</v>
       </c>
       <c r="P3" t="n">
-        <v>379.6707034897358</v>
+        <v>379.7207657884473</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32591,7 +32621,7 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3181293415956258</v>
+        <v>-0.3222924464135311</v>
       </c>
       <c r="J4" t="n">
         <v>465</v>
@@ -32600,19 +32630,19 @@
         <v>464</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05206675788967263</v>
+        <v>0.05353249352456657</v>
       </c>
       <c r="M4" t="n">
-        <v>8.636864004785243</v>
+        <v>8.620337707365543</v>
       </c>
       <c r="N4" t="n">
-        <v>104.3194894131988</v>
+        <v>103.9883133355196</v>
       </c>
       <c r="O4" t="n">
-        <v>10.2136912726594</v>
+        <v>10.19746602522017</v>
       </c>
       <c r="P4" t="n">
-        <v>387.1721208687022</v>
+        <v>387.2151303041136</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32669,7 +32699,7 @@
         <v>0.091</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2706128817441038</v>
+        <v>-0.2734207087976819</v>
       </c>
       <c r="J5" t="n">
         <v>465</v>
@@ -32678,19 +32708,19 @@
         <v>465</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04247641357622201</v>
+        <v>0.0435096390448283</v>
       </c>
       <c r="M5" t="n">
-        <v>7.770683106114359</v>
+        <v>7.758461481908004</v>
       </c>
       <c r="N5" t="n">
-        <v>93.37269471524175</v>
+        <v>92.96821778580257</v>
       </c>
       <c r="O5" t="n">
-        <v>9.662954761109138</v>
+        <v>9.642002789140987</v>
       </c>
       <c r="P5" t="n">
-        <v>386.2662067380584</v>
+        <v>386.2950469367276</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32747,7 +32777,7 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2675390203944811</v>
+        <v>-0.2725117869469647</v>
       </c>
       <c r="J6" t="n">
         <v>465</v>
@@ -32756,19 +32786,19 @@
         <v>465</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05501549779518911</v>
+        <v>0.05709477376626382</v>
       </c>
       <c r="M6" t="n">
-        <v>6.466561052488833</v>
+        <v>6.439825592239162</v>
       </c>
       <c r="N6" t="n">
-        <v>69.54008622002311</v>
+        <v>69.37753227584814</v>
       </c>
       <c r="O6" t="n">
-        <v>8.339069865400043</v>
+        <v>8.329317635667891</v>
       </c>
       <c r="P6" t="n">
-        <v>385.0121044742915</v>
+        <v>385.0635356532088</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32825,7 +32855,7 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06863168168058516</v>
+        <v>-0.07643951207957519</v>
       </c>
       <c r="J7" t="n">
         <v>465</v>
@@ -32834,19 +32864,19 @@
         <v>464</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002956759175434809</v>
+        <v>0.003647501860653768</v>
       </c>
       <c r="M7" t="n">
-        <v>7.148656648818556</v>
+        <v>7.189344671767859</v>
       </c>
       <c r="N7" t="n">
-        <v>89.68382237048871</v>
+        <v>90.13126274109766</v>
       </c>
       <c r="O7" t="n">
-        <v>9.470154294967358</v>
+        <v>9.493748613750927</v>
       </c>
       <c r="P7" t="n">
-        <v>381.2814051711675</v>
+        <v>381.3626341295179</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32903,7 +32933,7 @@
         <v>0.0788</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1164440705494926</v>
+        <v>-0.1165285188956287</v>
       </c>
       <c r="J8" t="n">
         <v>465</v>
@@ -32912,19 +32942,19 @@
         <v>465</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009307644797326375</v>
+        <v>0.009321995906721559</v>
       </c>
       <c r="M8" t="n">
-        <v>7.474157025712743</v>
+        <v>7.474299539297458</v>
       </c>
       <c r="N8" t="n">
-        <v>81.63099469031881</v>
+        <v>81.63279082165432</v>
       </c>
       <c r="O8" t="n">
-        <v>9.034987254574231</v>
+        <v>9.035086652692065</v>
       </c>
       <c r="P8" t="n">
-        <v>381.4716040379233</v>
+        <v>381.4728435942953</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32981,7 +33011,7 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1865010508801631</v>
+        <v>-0.2076836346177766</v>
       </c>
       <c r="J9" t="n">
         <v>465</v>
@@ -32990,19 +33020,19 @@
         <v>465</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02178928642184119</v>
+        <v>0.0270501218874013</v>
       </c>
       <c r="M9" t="n">
-        <v>7.611879229128529</v>
+        <v>7.597218959689272</v>
       </c>
       <c r="N9" t="n">
-        <v>88.3228947235788</v>
+        <v>87.76116334466158</v>
       </c>
       <c r="O9" t="n">
-        <v>9.398026107836623</v>
+        <v>9.368092833904967</v>
       </c>
       <c r="P9" t="n">
-        <v>375.1019629372263</v>
+        <v>375.321461594913</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33059,7 +33089,7 @@
         <v>0.1006</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5696812583289584</v>
+        <v>-0.5799209764546458</v>
       </c>
       <c r="J10" t="n">
         <v>465</v>
@@ -33068,19 +33098,19 @@
         <v>465</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1851373501425145</v>
+        <v>0.1902880954098627</v>
       </c>
       <c r="M10" t="n">
-        <v>7.342562248388093</v>
+        <v>7.351544495251345</v>
       </c>
       <c r="N10" t="n">
-        <v>80.79333829560626</v>
+        <v>80.95303206118545</v>
       </c>
       <c r="O10" t="n">
-        <v>8.988511461616225</v>
+        <v>8.997390291700446</v>
       </c>
       <c r="P10" t="n">
-        <v>376.0646272826585</v>
+        <v>376.1707549104344</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33137,7 +33167,7 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4023829556693571</v>
+        <v>-0.3999757425612319</v>
       </c>
       <c r="J11" t="n">
         <v>465</v>
@@ -33146,19 +33176,19 @@
         <v>465</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09903720756422851</v>
+        <v>0.09818825001784903</v>
       </c>
       <c r="M11" t="n">
-        <v>7.424122272387859</v>
+        <v>7.411539799601477</v>
       </c>
       <c r="N11" t="n">
-        <v>83.31226520030152</v>
+        <v>83.11898955869756</v>
       </c>
       <c r="O11" t="n">
-        <v>9.127555269638279</v>
+        <v>9.116961640738518</v>
       </c>
       <c r="P11" t="n">
-        <v>373.0014540748934</v>
+        <v>372.9767348347536</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33215,7 +33245,7 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6496805990873478</v>
+        <v>-0.6484192792033501</v>
       </c>
       <c r="J12" t="n">
         <v>465</v>
@@ -33224,19 +33254,19 @@
         <v>465</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2543520311676395</v>
+        <v>0.2537901996391876</v>
       </c>
       <c r="M12" t="n">
-        <v>6.882305108812364</v>
+        <v>6.87596384948672</v>
       </c>
       <c r="N12" t="n">
-        <v>69.98738155250851</v>
+        <v>69.93176957887324</v>
       </c>
       <c r="O12" t="n">
-        <v>8.365846134881307</v>
+        <v>8.362521723671231</v>
       </c>
       <c r="P12" t="n">
-        <v>379.0860136399741</v>
+        <v>379.0730676939639</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33293,7 +33323,7 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4921381636856249</v>
+        <v>-0.4904814345561994</v>
       </c>
       <c r="J13" t="n">
         <v>465</v>
@@ -33302,19 +33332,19 @@
         <v>465</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1292247447807257</v>
+        <v>0.1285581044632336</v>
       </c>
       <c r="M13" t="n">
-        <v>7.798754459826018</v>
+        <v>7.791327630877374</v>
       </c>
       <c r="N13" t="n">
-        <v>92.31149946825531</v>
+        <v>92.24879464882376</v>
       </c>
       <c r="O13" t="n">
-        <v>9.607887357179793</v>
+        <v>9.60462360786844</v>
       </c>
       <c r="P13" t="n">
-        <v>380.8819823078512</v>
+        <v>380.8649209670632</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33371,7 +33401,7 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3917268504311812</v>
+        <v>-0.3904731549954626</v>
       </c>
       <c r="J14" t="n">
         <v>465</v>
@@ -33380,19 +33410,19 @@
         <v>463</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08880071140063972</v>
+        <v>0.08832079966705386</v>
       </c>
       <c r="M14" t="n">
-        <v>7.939237956452233</v>
+        <v>7.93262012461596</v>
       </c>
       <c r="N14" t="n">
-        <v>89.29465098317063</v>
+        <v>89.26444335613419</v>
       </c>
       <c r="O14" t="n">
-        <v>9.449584698978608</v>
+        <v>9.44798620638992</v>
       </c>
       <c r="P14" t="n">
-        <v>383.6563300004973</v>
+        <v>383.6434099740306</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33449,7 +33479,7 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2634327312138645</v>
+        <v>-0.2625305547405877</v>
       </c>
       <c r="J15" t="n">
         <v>465</v>
@@ -33458,19 +33488,19 @@
         <v>461</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03693889184745813</v>
+        <v>0.03666797968250413</v>
       </c>
       <c r="M15" t="n">
-        <v>8.23049891381652</v>
+        <v>8.234635230237187</v>
       </c>
       <c r="N15" t="n">
-        <v>102.9531520650241</v>
+        <v>103.0467137200973</v>
       </c>
       <c r="O15" t="n">
-        <v>10.1465832704918</v>
+        <v>10.15119272401511</v>
       </c>
       <c r="P15" t="n">
-        <v>388.2873788970368</v>
+        <v>388.2777144414983</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33527,7 +33557,7 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3975024865313092</v>
+        <v>-0.3967082213825726</v>
       </c>
       <c r="J16" t="n">
         <v>465</v>
@@ -33536,19 +33566,19 @@
         <v>460</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05679256794996146</v>
+        <v>0.05654301224787228</v>
       </c>
       <c r="M16" t="n">
-        <v>10.11340197515838</v>
+        <v>10.11668854969283</v>
       </c>
       <c r="N16" t="n">
-        <v>149.422303572836</v>
+        <v>149.5411869132825</v>
       </c>
       <c r="O16" t="n">
-        <v>12.22384160453807</v>
+        <v>12.22870340278488</v>
       </c>
       <c r="P16" t="n">
-        <v>396.243472977157</v>
+        <v>396.2347508269295</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -73900,169 +73930,169 @@
     <row r="465">
       <c r="A465" s="1" t="inlineStr">
         <is>
-          <t>2026-03-27 22:26:53+00:00</t>
+          <t>2026-04-20 22:26:29+00:00</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>-45.503973601482876,166.71817028938298</t>
+          <t>-45.50400977434024,166.7182178627284</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>-45.503500514842244,166.7187679976958</t>
+          <t>-45.50349939474039,166.7187665245722</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>-45.502989143824955,166.71931536005414</t>
+          <t>-45.5029904615865,166.7193170931352</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>-45.502518751931,166.71991662143773</t>
+          <t>-45.50250689213056,166.71990102373894</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>-45.50207734708199,166.7205560105613</t>
+          <t>-45.502115561792905,166.720606269821</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>-45.501666668805356,166.7212230920862</t>
+          <t>-45.50172536071338,166.72130329770337</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>-45.50129257354692,166.72190971484474</t>
+          <t>-45.50129316508627,166.72191067460264</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>-45.50073083068485,166.72230273711537</t>
+          <t>-45.500828753928474,166.72248463571515</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>-45.500268548332755,166.7229165778354</t>
+          <t>-45.50034083098902,166.72305084793823</t>
         </is>
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>-45.499817280038926,166.7235508874949</t>
+          <t>-45.49980686049559,166.72353153241028</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>-45.49927768722838,166.7240190028284</t>
+          <t>-45.49927157218857,166.7240074985789</t>
         </is>
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>-45.4987240705388,166.72444873315362</t>
+          <t>-45.49871654276721,166.72443379580642</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
         <is>
-          <t>-45.498154651385775,166.7248408464459</t>
+          <t>-45.498149311413535,166.72482980595257</t>
         </is>
       </c>
       <c r="O465" t="inlineStr">
         <is>
-          <t>-45.49751013000752,166.7250876336817</t>
+          <t>-45.49750758717046,166.7250823763555</t>
         </is>
       </c>
       <c r="P465" t="inlineStr">
         <is>
-          <t>-45.4969219535359,166.72545092575297</t>
+          <t>-45.49692002098857,166.72544693021615</t>
         </is>
       </c>
       <c r="Q465" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L8</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="1" t="inlineStr">
         <is>
-          <t>2026-04-12 22:26:45+00:00</t>
+          <t>2026-05-14 22:26:25+00:00</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>-45.503973601482876,166.71817028938298</t>
+          <t>-45.504006216355016,166.71821318338027</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>-45.5034189450289,166.71866071979042</t>
+          <t>-45.50349662742982,166.71876288509068</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>-45.50293182117667,166.71923997110522</t>
+          <t>-45.50299724805806,166.7193260185041</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>-45.502451414595605,166.7198280612572</t>
+          <t>-45.50250886876409,166.71990362335495</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>-45.50207734708199,166.7205560105613</t>
+          <t>-45.50211872438882,166.72061042921106</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>-45.501666668805356,166.7212230920862</t>
+          <t>-45.50172911388779,166.72130842662395</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>-45.50129257354692,166.72190971484474</t>
+          <t>-45.50129233693118,166.72190933094157</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>-45.500643817892104,166.72214110631222</t>
+          <t>-45.500824607879956,166.7224769341457</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>-45.500268548332755,166.7229165778354</t>
+          <t>-45.500331338784086,166.72303321546687</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>-45.499817280038926,166.7235508874949</t>
+          <t>-45.49979584087065,166.7235110626429</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>-45.49927768722838,166.7240190028284</t>
+          <t>-45.49926762176408,166.72400006663148</t>
         </is>
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>-45.4987240705388,166.72444873315362</t>
+          <t>-45.498710844661154,166.72442248906717</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
         <is>
-          <t>-45.498154651385775,166.7248408464459</t>
+          <t>-45.498144734293696,166.72482034267432</t>
         </is>
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>-45.49751013000752,166.7250876336817</t>
+          <t>-45.49750255235244,166.72507196685103</t>
         </is>
       </c>
       <c r="P466" t="inlineStr">
         <is>
-          <t>-45.4969219535359,166.72545092575297</t>
+          <t>-45.49691559647183,166.7254377825408</t>
         </is>
       </c>
       <c r="Q466" t="inlineStr">

--- a/data/nzd0491/nzd0491.xlsx
+++ b/data/nzd0491/nzd0491.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q466"/>
+  <dimension ref="A1:Q467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26982,12 +26982,69 @@
         <v>372.14</v>
       </c>
       <c r="O466" t="n">
-        <v>392.84</v>
+        <v>390.18</v>
       </c>
       <c r="P466" t="n">
         <v>402.68</v>
       </c>
       <c r="Q466" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:26:15+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>365.33</v>
+      </c>
+      <c r="C467" t="n">
+        <v>375.04</v>
+      </c>
+      <c r="D467" t="n">
+        <v>382.91</v>
+      </c>
+      <c r="E467" t="n">
+        <v>387.96</v>
+      </c>
+      <c r="F467" t="n">
+        <v>377.74</v>
+      </c>
+      <c r="G467" t="n">
+        <v>369.71</v>
+      </c>
+      <c r="H467" t="n">
+        <v>370.25</v>
+      </c>
+      <c r="I467" t="n">
+        <v>361.25</v>
+      </c>
+      <c r="J467" t="n">
+        <v>354.28</v>
+      </c>
+      <c r="K467" t="n">
+        <v>357.57</v>
+      </c>
+      <c r="L467" t="n">
+        <v>359.17</v>
+      </c>
+      <c r="M467" t="n">
+        <v>366.25</v>
+      </c>
+      <c r="N467" t="n">
+        <v>376.82</v>
+      </c>
+      <c r="O467" t="n">
+        <v>389.96</v>
+      </c>
+      <c r="P467" t="n">
+        <v>402.11</v>
+      </c>
+      <c r="Q467" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27004,7 +27061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32297,6 +32354,16 @@
       </c>
       <c r="B529" t="n">
         <v>-0.72</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -32465,28 +32532,28 @@
         <v>0.153</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2858584131027693</v>
+        <v>-0.2877948329226885</v>
       </c>
       <c r="J2" t="n">
+        <v>466</v>
+      </c>
+      <c r="K2" t="n">
         <v>465</v>
       </c>
-      <c r="K2" t="n">
-        <v>464</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.05150981522444886</v>
+        <v>0.05237427804892736</v>
       </c>
       <c r="M2" t="n">
-        <v>7.802454771234358</v>
+        <v>7.795415892683561</v>
       </c>
       <c r="N2" t="n">
-        <v>85.17501144761505</v>
+        <v>85.03803006015012</v>
       </c>
       <c r="O2" t="n">
-        <v>9.229030905117559</v>
+        <v>9.221606696240634</v>
       </c>
       <c r="P2" t="n">
-        <v>377.5731719928133</v>
+        <v>377.5933468821265</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32543,28 +32610,28 @@
         <v>0.0901</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.091269917308515</v>
+        <v>-0.09220905406914141</v>
       </c>
       <c r="J3" t="n">
+        <v>466</v>
+      </c>
+      <c r="K3" t="n">
         <v>465</v>
       </c>
-      <c r="K3" t="n">
-        <v>464</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.005122861715456173</v>
+        <v>0.005251610720559574</v>
       </c>
       <c r="M3" t="n">
-        <v>8.021057997321327</v>
+        <v>8.008558904886016</v>
       </c>
       <c r="N3" t="n">
-        <v>91.60267936784395</v>
+        <v>91.41655258104676</v>
       </c>
       <c r="O3" t="n">
-        <v>9.570928866512588</v>
+        <v>9.561200373438826</v>
       </c>
       <c r="P3" t="n">
-        <v>379.7207657884473</v>
+        <v>379.7305481907049</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32621,28 +32688,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3222924464135311</v>
+        <v>-0.3205213655329354</v>
       </c>
       <c r="J4" t="n">
+        <v>466</v>
+      </c>
+      <c r="K4" t="n">
         <v>465</v>
       </c>
-      <c r="K4" t="n">
-        <v>464</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.05353249352456657</v>
+        <v>0.05318912972975598</v>
       </c>
       <c r="M4" t="n">
-        <v>8.620337707365543</v>
+        <v>8.608634076702938</v>
       </c>
       <c r="N4" t="n">
-        <v>103.9883133355196</v>
+        <v>103.8033350581101</v>
       </c>
       <c r="O4" t="n">
-        <v>10.19746602522017</v>
+        <v>10.1883921723749</v>
       </c>
       <c r="P4" t="n">
-        <v>387.2151303041136</v>
+        <v>387.1966820585213</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32699,28 +32766,28 @@
         <v>0.091</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2734207087976819</v>
+        <v>-0.2697017972831169</v>
       </c>
       <c r="J5" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K5" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0435096390448283</v>
+        <v>0.04249643625506938</v>
       </c>
       <c r="M5" t="n">
-        <v>7.758461481908004</v>
+        <v>7.757509010196191</v>
       </c>
       <c r="N5" t="n">
-        <v>92.96821778580257</v>
+        <v>92.93880666266648</v>
       </c>
       <c r="O5" t="n">
-        <v>9.642002789140987</v>
+        <v>9.640477512170571</v>
       </c>
       <c r="P5" t="n">
-        <v>386.2950469367276</v>
+        <v>386.2563147812591</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32777,28 +32844,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2725117869469647</v>
+        <v>-0.272545882190312</v>
       </c>
       <c r="J6" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K6" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05709477376626382</v>
+        <v>0.05735645444151172</v>
       </c>
       <c r="M6" t="n">
-        <v>6.439825592239162</v>
+        <v>6.426170995689223</v>
       </c>
       <c r="N6" t="n">
-        <v>69.37753227584814</v>
+        <v>69.22866774801008</v>
       </c>
       <c r="O6" t="n">
-        <v>8.329317635667891</v>
+        <v>8.32037665902272</v>
       </c>
       <c r="P6" t="n">
-        <v>385.0635356532088</v>
+        <v>385.0638907523449</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32855,28 +32922,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.07643951207957519</v>
+        <v>-0.08045240087780001</v>
       </c>
       <c r="J7" t="n">
+        <v>466</v>
+      </c>
+      <c r="K7" t="n">
         <v>465</v>
       </c>
-      <c r="K7" t="n">
-        <v>464</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.003647501860653768</v>
+        <v>0.004048619359047656</v>
       </c>
       <c r="M7" t="n">
-        <v>7.189344671767859</v>
+        <v>7.195001049463114</v>
       </c>
       <c r="N7" t="n">
-        <v>90.13126274109766</v>
+        <v>90.13514583697996</v>
       </c>
       <c r="O7" t="n">
-        <v>9.493748613750927</v>
+        <v>9.493953119590383</v>
       </c>
       <c r="P7" t="n">
-        <v>381.3626341295179</v>
+        <v>381.4045104344016</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32933,28 +33000,28 @@
         <v>0.0788</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1165285188956287</v>
+        <v>-0.1199105017633771</v>
       </c>
       <c r="J8" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K8" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009321995906721559</v>
+        <v>0.009893655849006699</v>
       </c>
       <c r="M8" t="n">
-        <v>7.474299539297458</v>
+        <v>7.478930957053671</v>
       </c>
       <c r="N8" t="n">
-        <v>81.63279082165432</v>
+        <v>81.59828063726005</v>
       </c>
       <c r="O8" t="n">
-        <v>9.035086652692065</v>
+        <v>9.033176663680393</v>
       </c>
       <c r="P8" t="n">
-        <v>381.4728435942953</v>
+        <v>381.5080666658076</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33011,28 +33078,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2076836346177766</v>
+        <v>-0.2112424621939649</v>
       </c>
       <c r="J9" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K9" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0270501218874013</v>
+        <v>0.02803580582135157</v>
       </c>
       <c r="M9" t="n">
-        <v>7.597218959689272</v>
+        <v>7.59858328597312</v>
       </c>
       <c r="N9" t="n">
-        <v>87.76116334466158</v>
+        <v>87.72859784252891</v>
       </c>
       <c r="O9" t="n">
-        <v>9.368092833904967</v>
+        <v>9.366354565279329</v>
       </c>
       <c r="P9" t="n">
-        <v>375.321461594913</v>
+        <v>375.3585264894197</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33089,28 +33156,28 @@
         <v>0.1006</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5799209764546458</v>
+        <v>-0.5826176121572341</v>
       </c>
       <c r="J10" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K10" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1902880954098627</v>
+        <v>0.1922638213494091</v>
       </c>
       <c r="M10" t="n">
-        <v>7.351544495251345</v>
+        <v>7.348471102099638</v>
       </c>
       <c r="N10" t="n">
-        <v>80.95303206118545</v>
+        <v>80.8687456257064</v>
       </c>
       <c r="O10" t="n">
-        <v>8.997390291700446</v>
+        <v>8.992705133924185</v>
       </c>
       <c r="P10" t="n">
-        <v>376.1707549104344</v>
+        <v>376.1988401479738</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33167,28 +33234,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3999757425612319</v>
+        <v>-0.4019669038444031</v>
       </c>
       <c r="J11" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K11" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09818825001784903</v>
+        <v>0.09942992143858642</v>
       </c>
       <c r="M11" t="n">
-        <v>7.411539799601477</v>
+        <v>7.405713516638071</v>
       </c>
       <c r="N11" t="n">
-        <v>83.11898955869756</v>
+        <v>82.98938263694801</v>
       </c>
       <c r="O11" t="n">
-        <v>9.116961640738518</v>
+        <v>9.109850857009022</v>
       </c>
       <c r="P11" t="n">
-        <v>372.9767348347536</v>
+        <v>372.9974726146338</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33245,28 +33312,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6484192792033501</v>
+        <v>-0.6495344207851929</v>
       </c>
       <c r="J12" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K12" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2537901996391876</v>
+        <v>0.2552735936605345</v>
       </c>
       <c r="M12" t="n">
-        <v>6.87596384948672</v>
+        <v>6.866633651869824</v>
       </c>
       <c r="N12" t="n">
-        <v>69.93176957887324</v>
+        <v>69.79699504568192</v>
       </c>
       <c r="O12" t="n">
-        <v>8.362521723671231</v>
+        <v>8.354459590283618</v>
       </c>
       <c r="P12" t="n">
-        <v>379.0730676939639</v>
+        <v>379.0846818011962</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33323,28 +33390,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4904814345561994</v>
+        <v>-0.4911408497306856</v>
       </c>
       <c r="J13" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K13" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1285581044632336</v>
+        <v>0.1293701871041263</v>
       </c>
       <c r="M13" t="n">
-        <v>7.791327630877374</v>
+        <v>7.777483426382324</v>
       </c>
       <c r="N13" t="n">
-        <v>92.24879464882376</v>
+        <v>92.0561835833709</v>
       </c>
       <c r="O13" t="n">
-        <v>9.60462360786844</v>
+        <v>9.594591371359746</v>
       </c>
       <c r="P13" t="n">
-        <v>380.8649209670632</v>
+        <v>380.8717887215006</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33401,28 +33468,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3904731549954626</v>
+        <v>-0.388994423117471</v>
       </c>
       <c r="J14" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K14" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08832079966705386</v>
+        <v>0.08805539982050548</v>
       </c>
       <c r="M14" t="n">
-        <v>7.93262012461596</v>
+        <v>7.923149538290321</v>
       </c>
       <c r="N14" t="n">
-        <v>89.26444335613419</v>
+        <v>89.09907988934228</v>
       </c>
       <c r="O14" t="n">
-        <v>9.44798620638992</v>
+        <v>9.439230895011642</v>
       </c>
       <c r="P14" t="n">
-        <v>383.6434099740306</v>
+        <v>383.6280130871448</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33479,28 +33546,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2625305547405877</v>
+        <v>-0.2600322487821015</v>
       </c>
       <c r="J15" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K15" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03666797968250413</v>
+        <v>0.03614283430980203</v>
       </c>
       <c r="M15" t="n">
-        <v>8.234635230237187</v>
+        <v>8.229026843243057</v>
       </c>
       <c r="N15" t="n">
-        <v>103.0467137200973</v>
+        <v>102.8678172988475</v>
       </c>
       <c r="O15" t="n">
-        <v>10.15119272401511</v>
+        <v>10.1423773001623</v>
       </c>
       <c r="P15" t="n">
-        <v>388.2777144414983</v>
+        <v>388.2517019250015</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33557,28 +33624,28 @@
         <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3967082213825726</v>
+        <v>-0.3898760121400416</v>
       </c>
       <c r="J16" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K16" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05654301224787228</v>
+        <v>0.05475375362191726</v>
       </c>
       <c r="M16" t="n">
-        <v>10.11668854969283</v>
+        <v>10.1268630854365</v>
       </c>
       <c r="N16" t="n">
-        <v>149.5411869132825</v>
+        <v>149.7974993733445</v>
       </c>
       <c r="O16" t="n">
-        <v>12.22870340278488</v>
+        <v>12.23917886842677</v>
       </c>
       <c r="P16" t="n">
-        <v>396.2347508269295</v>
+        <v>396.1636508014639</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33616,7 +33683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q466"/>
+  <dimension ref="A1:Q467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74087,7 +74154,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>-45.49750255235244,166.72507196685103</t>
+          <t>-45.4975160802454,166.72509993582696</t>
         </is>
       </c>
       <c r="P466" t="inlineStr">
@@ -74096,6 +74163,93 @@
         </is>
       </c>
       <c r="Q466" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-30 22:26:15+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>-45.504005886911926,166.7182127501073</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>-45.50349063158992,166.7187549995486</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>-45.502987496623014,166.7193131937029</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>-45.50250293886334,166.7198958245075</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>-45.50211898793848,166.7206107758269</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>-45.50172380767564,166.72130117539163</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>-45.50126926689078,166.72187190039915</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>-45.500811896965125,166.72245332276242</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>-45.50033046593754,166.72303159409051</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>-45.4997930586876,166.7235058945346</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>-45.49926561949397,166.72399629975442</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>-45.49870812629828,166.72441709502726</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>-45.49812093325912,166.7247711336529</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>-45.4975171990934,166.72510224905116</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>-45.496918495293215,166.72544377584518</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
